--- a/Solutions/Metabasite.xlsx
+++ b/Solutions/Metabasite.xlsx
@@ -1,31 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Thermolab-main\v_24_03_18\Solutions\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dropbox\Thermolab\v_25_10_01\Solutions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45547E9C-362C-4FA1-AFC9-0A7354F9F4DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{973424CC-BF31-4422-BCC0-51F0757452B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{A49E5DA2-E197-42C8-A9DC-E0DBAA94DA8C}"/>
+    <workbookView xWindow="46680" yWindow="2355" windowWidth="28800" windowHeight="15435" activeTab="3" xr2:uid="{A49E5DA2-E197-42C8-A9DC-E0DBAA94DA8C}"/>
   </bookViews>
   <sheets>
     <sheet name="Amphibole" sheetId="1" r:id="rId1"/>
-    <sheet name="Clinopyroxene" sheetId="2" r:id="rId2"/>
-    <sheet name="Orthopyroxene" sheetId="11" r:id="rId3"/>
-    <sheet name="Garnet" sheetId="3" r:id="rId4"/>
-    <sheet name="Epidote" sheetId="4" r:id="rId5"/>
-    <sheet name="Muscovite" sheetId="5" r:id="rId6"/>
-    <sheet name="Biotite" sheetId="7" r:id="rId7"/>
-    <sheet name="Chlorite" sheetId="10" r:id="rId8"/>
-    <sheet name="Feldspar" sheetId="8" r:id="rId9"/>
-    <sheet name="Feldspar(I1)" sheetId="6" r:id="rId10"/>
-    <sheet name="Ilmenite" sheetId="12" r:id="rId11"/>
-    <sheet name="Olivine" sheetId="13" r:id="rId12"/>
-    <sheet name="Spinel" sheetId="14" r:id="rId13"/>
+    <sheet name="Melt(G16)" sheetId="15" r:id="rId2"/>
+    <sheet name="Augite" sheetId="16" r:id="rId3"/>
+    <sheet name="Diopside" sheetId="2" r:id="rId4"/>
+    <sheet name="Orthopyroxene" sheetId="11" r:id="rId5"/>
+    <sheet name="Garnet" sheetId="3" r:id="rId6"/>
+    <sheet name="Epidote" sheetId="4" r:id="rId7"/>
+    <sheet name="Muscovite" sheetId="5" r:id="rId8"/>
+    <sheet name="Biotite" sheetId="7" r:id="rId9"/>
+    <sheet name="Chlorite" sheetId="10" r:id="rId10"/>
+    <sheet name="Feldspar" sheetId="8" r:id="rId11"/>
+    <sheet name="Feldspar(I1)" sheetId="6" r:id="rId12"/>
+    <sheet name="Ilmenite" sheetId="12" r:id="rId13"/>
+    <sheet name="Olivine" sheetId="13" r:id="rId14"/>
+    <sheet name="Spinel" sheetId="14" r:id="rId15"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,12 +43,15 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="645" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="856" uniqueCount="213">
   <si>
     <t>Modeltype</t>
   </si>
@@ -576,7 +581,115 @@
     <t>usp</t>
   </si>
   <si>
-    <t>Sp)</t>
+    <t>faq</t>
+  </si>
+  <si>
+    <t>q4L,tc-ds62</t>
+  </si>
+  <si>
+    <t>abL,tc-ds62</t>
+  </si>
+  <si>
+    <t>kspL,tc-ds62</t>
+  </si>
+  <si>
+    <t>h2oL,tc-ds62</t>
+  </si>
+  <si>
+    <t>q4L</t>
+  </si>
+  <si>
+    <t>abL</t>
+  </si>
+  <si>
+    <t>kspL</t>
+  </si>
+  <si>
+    <t>slL</t>
+  </si>
+  <si>
+    <t>fo2L</t>
+  </si>
+  <si>
+    <t>fa2L</t>
+  </si>
+  <si>
+    <t>h2oL</t>
+  </si>
+  <si>
+    <t>wo1L,tc-ds62</t>
+  </si>
+  <si>
+    <t>sl1L,tc-ds62</t>
+  </si>
+  <si>
+    <t>anoL,tc-ds62</t>
+  </si>
+  <si>
+    <t>Si4L</t>
+  </si>
+  <si>
+    <t>woL</t>
+  </si>
+  <si>
+    <t>silL</t>
+  </si>
+  <si>
+    <t>Si2L</t>
+  </si>
+  <si>
+    <t>anoL</t>
+  </si>
+  <si>
+    <t>fo2Lmb,tc-ds62</t>
+  </si>
+  <si>
+    <t>fa2Lmb,tc-ds62</t>
+  </si>
+  <si>
+    <t>pol</t>
+  </si>
+  <si>
+    <t>H2O</t>
+  </si>
+  <si>
+    <t>cenh,tc-ds62</t>
+  </si>
+  <si>
+    <t>cfs,tc-ds62</t>
+  </si>
+  <si>
+    <t>jdm,tc-ds62</t>
+  </si>
+  <si>
+    <t>ocats,tc-ds62</t>
+  </si>
+  <si>
+    <t>dcats,tc-ds62</t>
+  </si>
+  <si>
+    <t>fmc,tc-ds62</t>
+  </si>
+  <si>
+    <t>cenh</t>
+  </si>
+  <si>
+    <t>cfs</t>
+  </si>
+  <si>
+    <t>jdm</t>
+  </si>
+  <si>
+    <t>ocats</t>
+  </si>
+  <si>
+    <t>dcats</t>
+  </si>
+  <si>
+    <t>fmc</t>
+  </si>
+  <si>
+    <t>acmm2,tc-ds62</t>
   </si>
 </sst>
 </file>
@@ -616,7 +729,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -624,6 +737,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1981,7 +2095,7 @@
         <v>0</v>
       </c>
       <c r="D23">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -2002,7 +2116,7 @@
         <v>0</v>
       </c>
       <c r="K23">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L23">
         <v>0</v>
@@ -2643,6 +2757,1223 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8EC04B4-F8B6-4270-845C-06CD900EF148}">
+  <dimension ref="A1:L28"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="13.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D3" t="s">
+        <v>73</v>
+      </c>
+      <c r="E3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F3" t="s">
+        <v>129</v>
+      </c>
+      <c r="G3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K3" t="s">
+        <v>130</v>
+      </c>
+      <c r="L3" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4" t="s">
+        <v>15</v>
+      </c>
+      <c r="J4" t="s">
+        <v>14</v>
+      </c>
+      <c r="K4" t="s">
+        <v>18</v>
+      </c>
+      <c r="L4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>138</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>4</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>1</v>
+      </c>
+      <c r="K6">
+        <v>1</v>
+      </c>
+      <c r="L6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>139</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>4</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>2</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>140</v>
+      </c>
+      <c r="B8">
+        <v>0</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8">
+        <v>4</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>1</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>141</v>
+      </c>
+      <c r="B9">
+        <v>0</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>4</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>1</v>
+      </c>
+      <c r="K9">
+        <v>1</v>
+      </c>
+      <c r="L9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>142</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>4</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>1</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>2</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>143</v>
+      </c>
+      <c r="B11">
+        <v>0</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>4</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>2</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>144</v>
+      </c>
+      <c r="B12">
+        <v>1</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>4</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>1</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>1</v>
+      </c>
+      <c r="L12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14">
+        <v>1</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
+      <c r="D14">
+        <v>1</v>
+      </c>
+      <c r="E14">
+        <v>4</v>
+      </c>
+      <c r="F14">
+        <v>4</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+      <c r="H14">
+        <v>1</v>
+      </c>
+      <c r="I14">
+        <v>1</v>
+      </c>
+      <c r="J14">
+        <v>1</v>
+      </c>
+      <c r="K14">
+        <v>2</v>
+      </c>
+      <c r="L14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>22</v>
+      </c>
+      <c r="B16">
+        <v>0</v>
+      </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
+      <c r="D16">
+        <v>0</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <v>0</v>
+      </c>
+      <c r="L16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>23</v>
+      </c>
+      <c r="B17">
+        <v>1</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
+      <c r="D17">
+        <v>1</v>
+      </c>
+      <c r="E17">
+        <v>1</v>
+      </c>
+      <c r="F17">
+        <v>1</v>
+      </c>
+      <c r="G17">
+        <v>1</v>
+      </c>
+      <c r="H17">
+        <v>1</v>
+      </c>
+      <c r="I17">
+        <v>1</v>
+      </c>
+      <c r="J17">
+        <v>1</v>
+      </c>
+      <c r="K17">
+        <v>1</v>
+      </c>
+      <c r="L17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>24</v>
+      </c>
+      <c r="B18">
+        <f>1/15</f>
+        <v>6.6666666666666666E-2</v>
+      </c>
+      <c r="C18">
+        <f t="shared" ref="C18:L18" si="0">1/15</f>
+        <v>6.6666666666666666E-2</v>
+      </c>
+      <c r="D18">
+        <f t="shared" si="0"/>
+        <v>6.6666666666666666E-2</v>
+      </c>
+      <c r="E18">
+        <f t="shared" si="0"/>
+        <v>6.6666666666666666E-2</v>
+      </c>
+      <c r="F18">
+        <f t="shared" si="0"/>
+        <v>6.6666666666666666E-2</v>
+      </c>
+      <c r="G18">
+        <f t="shared" si="0"/>
+        <v>6.6666666666666666E-2</v>
+      </c>
+      <c r="H18">
+        <f t="shared" si="0"/>
+        <v>6.6666666666666666E-2</v>
+      </c>
+      <c r="I18">
+        <f t="shared" si="0"/>
+        <v>6.6666666666666666E-2</v>
+      </c>
+      <c r="J18">
+        <f t="shared" si="0"/>
+        <v>6.6666666666666666E-2</v>
+      </c>
+      <c r="K18">
+        <f t="shared" si="0"/>
+        <v>6.6666666666666666E-2</v>
+      </c>
+      <c r="L18">
+        <f t="shared" si="0"/>
+        <v>6.6666666666666666E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>25</v>
+      </c>
+      <c r="B19">
+        <v>0</v>
+      </c>
+      <c r="C19">
+        <v>0</v>
+      </c>
+      <c r="D19">
+        <v>0</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19">
+        <v>0</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19">
+        <v>0</v>
+      </c>
+      <c r="L19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>26</v>
+      </c>
+      <c r="B21" t="s">
+        <v>131</v>
+      </c>
+      <c r="C21" t="s">
+        <v>132</v>
+      </c>
+      <c r="D21" t="s">
+        <v>133</v>
+      </c>
+      <c r="E21" t="s">
+        <v>134</v>
+      </c>
+      <c r="F21" t="s">
+        <v>135</v>
+      </c>
+      <c r="G21" t="s">
+        <v>136</v>
+      </c>
+      <c r="H21" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>131</v>
+      </c>
+      <c r="B22">
+        <v>0</v>
+      </c>
+      <c r="C22">
+        <v>17000</v>
+      </c>
+      <c r="D22">
+        <v>17000</v>
+      </c>
+      <c r="E22">
+        <v>20000</v>
+      </c>
+      <c r="F22">
+        <v>30000</v>
+      </c>
+      <c r="G22">
+        <v>21000</v>
+      </c>
+      <c r="H22">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>132</v>
+      </c>
+      <c r="B23">
+        <v>17000</v>
+      </c>
+      <c r="C23">
+        <v>0</v>
+      </c>
+      <c r="D23">
+        <v>16000</v>
+      </c>
+      <c r="E23">
+        <v>37000</v>
+      </c>
+      <c r="F23">
+        <v>20000</v>
+      </c>
+      <c r="G23">
+        <v>4000</v>
+      </c>
+      <c r="H23">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>133</v>
+      </c>
+      <c r="B24">
+        <v>17000</v>
+      </c>
+      <c r="C24">
+        <v>16000</v>
+      </c>
+      <c r="D24">
+        <v>0</v>
+      </c>
+      <c r="E24">
+        <v>30000</v>
+      </c>
+      <c r="F24">
+        <v>29000</v>
+      </c>
+      <c r="G24">
+        <v>13000</v>
+      </c>
+      <c r="H24">
+        <v>19000</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>134</v>
+      </c>
+      <c r="B25">
+        <v>20000</v>
+      </c>
+      <c r="C25">
+        <v>37000</v>
+      </c>
+      <c r="D25">
+        <v>30000</v>
+      </c>
+      <c r="E25">
+        <v>0</v>
+      </c>
+      <c r="F25">
+        <v>18000</v>
+      </c>
+      <c r="G25">
+        <v>33000</v>
+      </c>
+      <c r="H25">
+        <v>22000</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>135</v>
+      </c>
+      <c r="B26">
+        <v>30000</v>
+      </c>
+      <c r="C26">
+        <v>20000</v>
+      </c>
+      <c r="D26">
+        <v>29000</v>
+      </c>
+      <c r="E26">
+        <v>18000</v>
+      </c>
+      <c r="F26">
+        <v>0</v>
+      </c>
+      <c r="G26">
+        <v>24000</v>
+      </c>
+      <c r="H26">
+        <v>28600</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>136</v>
+      </c>
+      <c r="B27">
+        <v>21000</v>
+      </c>
+      <c r="C27">
+        <v>4000</v>
+      </c>
+      <c r="D27">
+        <v>13000</v>
+      </c>
+      <c r="E27">
+        <v>33000</v>
+      </c>
+      <c r="F27">
+        <v>24000</v>
+      </c>
+      <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27">
+        <v>19000</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>137</v>
+      </c>
+      <c r="B28">
+        <v>2000</v>
+      </c>
+      <c r="C28">
+        <v>15000</v>
+      </c>
+      <c r="D28">
+        <v>19000</v>
+      </c>
+      <c r="E28">
+        <v>22000</v>
+      </c>
+      <c r="F28">
+        <v>28600</v>
+      </c>
+      <c r="G28">
+        <v>19000</v>
+      </c>
+      <c r="H28">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75EE02EB-ADA8-400E-A64B-539138E19798}">
+  <dimension ref="A1:F35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="11.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F3" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>127</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>109</v>
+      </c>
+      <c r="B7">
+        <v>0</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>2</v>
+      </c>
+      <c r="F7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>110</v>
+      </c>
+      <c r="B8">
+        <v>0</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+      <c r="F8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="E10">
+        <v>1</v>
+      </c>
+      <c r="F10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12">
+        <v>0</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>23</v>
+      </c>
+      <c r="B13">
+        <v>1</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
+      <c r="D13">
+        <v>1</v>
+      </c>
+      <c r="E13">
+        <v>1</v>
+      </c>
+      <c r="F13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>24</v>
+      </c>
+      <c r="B14">
+        <v>6.7000000000000004E-2</v>
+      </c>
+      <c r="C14">
+        <v>6.7000000000000004E-2</v>
+      </c>
+      <c r="D14">
+        <v>6.7000000000000004E-2</v>
+      </c>
+      <c r="E14">
+        <v>6.7000000000000004E-2</v>
+      </c>
+      <c r="F14">
+        <v>6.7000000000000004E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>25</v>
+      </c>
+      <c r="B15">
+        <v>0</v>
+      </c>
+      <c r="C15">
+        <v>0</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>26</v>
+      </c>
+      <c r="B17" t="s">
+        <v>111</v>
+      </c>
+      <c r="C17" t="s">
+        <v>106</v>
+      </c>
+      <c r="D17" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>111</v>
+      </c>
+      <c r="B18">
+        <v>0</v>
+      </c>
+      <c r="C18" s="5">
+        <v>14600</v>
+      </c>
+      <c r="D18" s="5">
+        <v>24100</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>106</v>
+      </c>
+      <c r="B19" s="5">
+        <v>14600</v>
+      </c>
+      <c r="C19">
+        <v>0</v>
+      </c>
+      <c r="D19" s="5">
+        <v>48500</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>107</v>
+      </c>
+      <c r="B20" s="5">
+        <v>24100</v>
+      </c>
+      <c r="C20" s="5">
+        <v>48500</v>
+      </c>
+      <c r="D20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>34</v>
+      </c>
+      <c r="B22" t="s">
+        <v>111</v>
+      </c>
+      <c r="C22" t="s">
+        <v>106</v>
+      </c>
+      <c r="D22" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>111</v>
+      </c>
+      <c r="B23">
+        <v>0</v>
+      </c>
+      <c r="C23">
+        <v>-9.35</v>
+      </c>
+      <c r="D23">
+        <v>-9.57</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>106</v>
+      </c>
+      <c r="B24">
+        <v>-9.35</v>
+      </c>
+      <c r="C24">
+        <v>0</v>
+      </c>
+      <c r="D24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>107</v>
+      </c>
+      <c r="B25">
+        <v>-9.57</v>
+      </c>
+      <c r="C25">
+        <v>0</v>
+      </c>
+      <c r="D25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>35</v>
+      </c>
+      <c r="B27" t="s">
+        <v>111</v>
+      </c>
+      <c r="C27" t="s">
+        <v>106</v>
+      </c>
+      <c r="D27" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>111</v>
+      </c>
+      <c r="B28">
+        <v>0</v>
+      </c>
+      <c r="C28">
+        <v>-40</v>
+      </c>
+      <c r="D28" s="5">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>106</v>
+      </c>
+      <c r="B29">
+        <v>-40</v>
+      </c>
+      <c r="C29">
+        <v>0</v>
+      </c>
+      <c r="D29">
+        <v>-130</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>107</v>
+      </c>
+      <c r="B30" s="5">
+        <v>338</v>
+      </c>
+      <c r="C30">
+        <v>-130</v>
+      </c>
+      <c r="D30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>36</v>
+      </c>
+      <c r="B32" t="s">
+        <v>111</v>
+      </c>
+      <c r="C32" t="s">
+        <v>106</v>
+      </c>
+      <c r="D32" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>37</v>
+      </c>
+      <c r="B33">
+        <v>0.67400000000000004</v>
+      </c>
+      <c r="C33">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="D33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>38</v>
+      </c>
+      <c r="B34">
+        <v>0</v>
+      </c>
+      <c r="C34">
+        <v>0</v>
+      </c>
+      <c r="D34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>39</v>
+      </c>
+      <c r="B35">
+        <v>0</v>
+      </c>
+      <c r="C35">
+        <v>0</v>
+      </c>
+      <c r="D35">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11D063D2-B63C-4FD4-B9C7-610F4E699550}">
   <dimension ref="A1:J35"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3032,7 +4363,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{562841B5-2CE3-4AF4-B924-12DA9A538BCD}">
   <dimension ref="A1:G24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3345,7 +4676,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A2380B6-156D-48B4-B01F-F11751B6C129}">
   <dimension ref="A1:E23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3550,7 +4881,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7CA70AFB-945D-490B-B834-AC2D41D28234}">
   <dimension ref="A1:F22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3699,8 +5030,8 @@
       <c r="E11">
         <v>1</v>
       </c>
-      <c r="F11" t="s">
-        <v>176</v>
+      <c r="F11">
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -3874,6 +5205,3334 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{235766CB-85E5-4E00-A98A-A35D6EFE0C78}">
+  <dimension ref="A1:O59"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="14.42578125" customWidth="1"/>
+    <col min="2" max="4" width="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.140625" customWidth="1"/>
+    <col min="7" max="8" width="9" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="C3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D3" t="s">
+        <v>73</v>
+      </c>
+      <c r="E3" t="s">
+        <v>73</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="I3" t="s">
+        <v>73</v>
+      </c>
+      <c r="J3" t="s">
+        <v>198</v>
+      </c>
+      <c r="K3" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="L3" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="N3" s="7"/>
+      <c r="O3" s="7"/>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>176</v>
+      </c>
+      <c r="C4" t="s">
+        <v>191</v>
+      </c>
+      <c r="D4" t="s">
+        <v>182</v>
+      </c>
+      <c r="E4" t="s">
+        <v>183</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>192</v>
+      </c>
+      <c r="G4" t="s">
+        <v>193</v>
+      </c>
+      <c r="H4" t="s">
+        <v>199</v>
+      </c>
+      <c r="I4" t="s">
+        <v>195</v>
+      </c>
+      <c r="J4" t="s">
+        <v>194</v>
+      </c>
+      <c r="K4" t="s">
+        <v>13</v>
+      </c>
+      <c r="L4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>177</v>
+      </c>
+      <c r="B6" s="6">
+        <v>1</v>
+      </c>
+      <c r="C6" s="6">
+        <v>1</v>
+      </c>
+      <c r="D6" s="6">
+        <v>0</v>
+      </c>
+      <c r="E6" s="6">
+        <v>0</v>
+      </c>
+      <c r="F6" s="6">
+        <v>0</v>
+      </c>
+      <c r="G6" s="6">
+        <v>0</v>
+      </c>
+      <c r="H6" s="6">
+        <v>0</v>
+      </c>
+      <c r="I6" s="6">
+        <v>0</v>
+      </c>
+      <c r="J6" s="6">
+        <v>0</v>
+      </c>
+      <c r="K6" s="6">
+        <v>0</v>
+      </c>
+      <c r="L6" s="6">
+        <v>0</v>
+      </c>
+      <c r="N6" s="6"/>
+      <c r="O6" s="6"/>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>178</v>
+      </c>
+      <c r="B7" s="6">
+        <v>1</v>
+      </c>
+      <c r="C7" s="6">
+        <v>0</v>
+      </c>
+      <c r="D7" s="6">
+        <v>1</v>
+      </c>
+      <c r="E7" s="6">
+        <v>0</v>
+      </c>
+      <c r="F7" s="6">
+        <v>0</v>
+      </c>
+      <c r="G7" s="6">
+        <v>0</v>
+      </c>
+      <c r="H7" s="6">
+        <v>0</v>
+      </c>
+      <c r="I7" s="6">
+        <v>0</v>
+      </c>
+      <c r="J7" s="6">
+        <v>0</v>
+      </c>
+      <c r="K7" s="6">
+        <v>0</v>
+      </c>
+      <c r="L7" s="6">
+        <v>0</v>
+      </c>
+      <c r="N7" s="6"/>
+      <c r="O7" s="6"/>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>179</v>
+      </c>
+      <c r="B8" s="6">
+        <v>1</v>
+      </c>
+      <c r="C8" s="6">
+        <v>0</v>
+      </c>
+      <c r="D8" s="6">
+        <v>0</v>
+      </c>
+      <c r="E8" s="6">
+        <v>1</v>
+      </c>
+      <c r="F8" s="6">
+        <v>0</v>
+      </c>
+      <c r="G8" s="6">
+        <v>0</v>
+      </c>
+      <c r="H8" s="6">
+        <v>0</v>
+      </c>
+      <c r="I8" s="6">
+        <v>0</v>
+      </c>
+      <c r="J8" s="6">
+        <v>0</v>
+      </c>
+      <c r="K8" s="6">
+        <v>0</v>
+      </c>
+      <c r="L8" s="6">
+        <v>0</v>
+      </c>
+      <c r="N8" s="6"/>
+      <c r="O8" s="6"/>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>188</v>
+      </c>
+      <c r="B9" s="6">
+        <v>1</v>
+      </c>
+      <c r="C9" s="6">
+        <v>0</v>
+      </c>
+      <c r="D9" s="6">
+        <v>0</v>
+      </c>
+      <c r="E9" s="6">
+        <v>0</v>
+      </c>
+      <c r="F9" s="6">
+        <v>1</v>
+      </c>
+      <c r="G9" s="6">
+        <v>0</v>
+      </c>
+      <c r="H9" s="6">
+        <v>0</v>
+      </c>
+      <c r="I9" s="6">
+        <v>0</v>
+      </c>
+      <c r="J9" s="6">
+        <v>0</v>
+      </c>
+      <c r="K9" s="6">
+        <v>0</v>
+      </c>
+      <c r="L9" s="6">
+        <v>0</v>
+      </c>
+      <c r="N9" s="6"/>
+      <c r="O9" s="6"/>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>189</v>
+      </c>
+      <c r="B10" s="6">
+        <v>1</v>
+      </c>
+      <c r="C10" s="6">
+        <v>0</v>
+      </c>
+      <c r="D10" s="6">
+        <v>0</v>
+      </c>
+      <c r="E10" s="6">
+        <v>0</v>
+      </c>
+      <c r="F10" s="6">
+        <v>0</v>
+      </c>
+      <c r="G10" s="6">
+        <v>1</v>
+      </c>
+      <c r="H10" s="6">
+        <v>0</v>
+      </c>
+      <c r="I10" s="6">
+        <v>0</v>
+      </c>
+      <c r="J10" s="6">
+        <v>0</v>
+      </c>
+      <c r="K10" s="6">
+        <v>0</v>
+      </c>
+      <c r="L10" s="6">
+        <v>0</v>
+      </c>
+      <c r="N10" s="6"/>
+      <c r="O10" s="6"/>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>197</v>
+      </c>
+      <c r="B11" s="6">
+        <v>1</v>
+      </c>
+      <c r="C11" s="6">
+        <v>0</v>
+      </c>
+      <c r="D11" s="6">
+        <v>0</v>
+      </c>
+      <c r="E11" s="6">
+        <v>0</v>
+      </c>
+      <c r="F11" s="6">
+        <v>0</v>
+      </c>
+      <c r="G11" s="6">
+        <v>0</v>
+      </c>
+      <c r="H11" s="6">
+        <v>0</v>
+      </c>
+      <c r="I11" s="6">
+        <v>0</v>
+      </c>
+      <c r="J11" s="6">
+        <v>1</v>
+      </c>
+      <c r="K11" s="6">
+        <v>1</v>
+      </c>
+      <c r="L11" s="6">
+        <v>0</v>
+      </c>
+      <c r="N11" s="6"/>
+      <c r="O11" s="6"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>196</v>
+      </c>
+      <c r="B12" s="6">
+        <v>1</v>
+      </c>
+      <c r="C12" s="6">
+        <v>0</v>
+      </c>
+      <c r="D12" s="6">
+        <v>0</v>
+      </c>
+      <c r="E12" s="6">
+        <v>0</v>
+      </c>
+      <c r="F12" s="6">
+        <v>0</v>
+      </c>
+      <c r="G12" s="6">
+        <v>0</v>
+      </c>
+      <c r="H12" s="6">
+        <v>0</v>
+      </c>
+      <c r="I12" s="6">
+        <v>0</v>
+      </c>
+      <c r="J12" s="6">
+        <v>1</v>
+      </c>
+      <c r="K12" s="6">
+        <v>0</v>
+      </c>
+      <c r="L12" s="6">
+        <v>1</v>
+      </c>
+      <c r="N12" s="6"/>
+      <c r="O12" s="6"/>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>180</v>
+      </c>
+      <c r="B13" s="6">
+        <v>0</v>
+      </c>
+      <c r="C13" s="6">
+        <v>0</v>
+      </c>
+      <c r="D13" s="6">
+        <v>0</v>
+      </c>
+      <c r="E13" s="6">
+        <v>0</v>
+      </c>
+      <c r="F13" s="6">
+        <v>0</v>
+      </c>
+      <c r="G13" s="6">
+        <v>0</v>
+      </c>
+      <c r="H13" s="6">
+        <v>1</v>
+      </c>
+      <c r="I13" s="6">
+        <v>0</v>
+      </c>
+      <c r="J13" s="6">
+        <v>0</v>
+      </c>
+      <c r="K13" s="6">
+        <v>0</v>
+      </c>
+      <c r="L13" s="6">
+        <v>0</v>
+      </c>
+      <c r="N13" s="6"/>
+      <c r="O13" s="6"/>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>190</v>
+      </c>
+      <c r="B14" s="6">
+        <v>1</v>
+      </c>
+      <c r="C14" s="6">
+        <v>0</v>
+      </c>
+      <c r="D14" s="6">
+        <v>0</v>
+      </c>
+      <c r="E14" s="6">
+        <v>0</v>
+      </c>
+      <c r="F14" s="6">
+        <v>0</v>
+      </c>
+      <c r="G14" s="6">
+        <v>0</v>
+      </c>
+      <c r="H14" s="6">
+        <v>0</v>
+      </c>
+      <c r="I14" s="6">
+        <v>1</v>
+      </c>
+      <c r="J14" s="6">
+        <v>0</v>
+      </c>
+      <c r="K14" s="6">
+        <v>0</v>
+      </c>
+      <c r="L14" s="6">
+        <v>0</v>
+      </c>
+      <c r="N14" s="6"/>
+      <c r="O14" s="6"/>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B16" s="6">
+        <v>1</v>
+      </c>
+      <c r="C16">
+        <v>1</v>
+      </c>
+      <c r="D16">
+        <v>1</v>
+      </c>
+      <c r="E16">
+        <v>1</v>
+      </c>
+      <c r="F16">
+        <v>1</v>
+      </c>
+      <c r="G16">
+        <v>1</v>
+      </c>
+      <c r="H16" s="6">
+        <v>2</v>
+      </c>
+      <c r="I16">
+        <v>1</v>
+      </c>
+      <c r="J16">
+        <v>-4</v>
+      </c>
+      <c r="K16" s="6">
+        <v>5</v>
+      </c>
+      <c r="L16">
+        <v>5</v>
+      </c>
+      <c r="N16" s="6"/>
+      <c r="O16" s="6"/>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>22</v>
+      </c>
+      <c r="B18" s="6">
+        <v>0</v>
+      </c>
+      <c r="C18" s="6">
+        <v>0</v>
+      </c>
+      <c r="D18" s="6">
+        <v>0</v>
+      </c>
+      <c r="E18" s="6">
+        <v>0</v>
+      </c>
+      <c r="F18" s="6">
+        <v>0</v>
+      </c>
+      <c r="G18" s="6">
+        <v>0</v>
+      </c>
+      <c r="H18" s="6">
+        <v>0</v>
+      </c>
+      <c r="I18" s="6">
+        <v>0</v>
+      </c>
+      <c r="J18" s="6">
+        <v>0</v>
+      </c>
+      <c r="K18" s="6">
+        <v>0</v>
+      </c>
+      <c r="L18" s="6">
+        <v>0</v>
+      </c>
+      <c r="N18" s="6"/>
+      <c r="O18" s="6"/>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>23</v>
+      </c>
+      <c r="B19" s="6">
+        <v>1</v>
+      </c>
+      <c r="C19" s="6">
+        <v>1</v>
+      </c>
+      <c r="D19" s="6">
+        <v>1</v>
+      </c>
+      <c r="E19" s="6">
+        <v>1</v>
+      </c>
+      <c r="F19" s="6">
+        <v>1</v>
+      </c>
+      <c r="G19" s="6">
+        <v>1</v>
+      </c>
+      <c r="H19" s="6">
+        <v>1</v>
+      </c>
+      <c r="I19" s="6">
+        <v>1</v>
+      </c>
+      <c r="J19" s="6">
+        <v>1</v>
+      </c>
+      <c r="K19" s="6">
+        <v>1</v>
+      </c>
+      <c r="L19" s="6">
+        <v>1</v>
+      </c>
+      <c r="N19" s="6"/>
+      <c r="O19" s="6"/>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>24</v>
+      </c>
+      <c r="B20" s="2">
+        <f t="shared" ref="B20:L20" si="0">1/6</f>
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="C20" s="2">
+        <f>1/6</f>
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="D20" s="2">
+        <f t="shared" si="0"/>
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="E20" s="2">
+        <f t="shared" si="0"/>
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="F20" s="2">
+        <f t="shared" si="0"/>
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="G20" s="2">
+        <f t="shared" si="0"/>
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="H20" s="2">
+        <f t="shared" si="0"/>
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="I20" s="2">
+        <f t="shared" si="0"/>
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="J20" s="2">
+        <f t="shared" si="0"/>
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="K20" s="2">
+        <f t="shared" si="0"/>
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="L20" s="2">
+        <f t="shared" si="0"/>
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="N20" s="2"/>
+      <c r="O20" s="2"/>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>25</v>
+      </c>
+      <c r="B21">
+        <v>0</v>
+      </c>
+      <c r="C21">
+        <v>0</v>
+      </c>
+      <c r="D21">
+        <v>0</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21">
+        <v>0</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21">
+        <v>0</v>
+      </c>
+      <c r="L21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="J22" s="6"/>
+      <c r="K22" s="6"/>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>26</v>
+      </c>
+      <c r="B23" t="s">
+        <v>181</v>
+      </c>
+      <c r="C23" t="s">
+        <v>182</v>
+      </c>
+      <c r="D23" t="s">
+        <v>183</v>
+      </c>
+      <c r="E23" t="s">
+        <v>192</v>
+      </c>
+      <c r="F23" t="s">
+        <v>184</v>
+      </c>
+      <c r="G23" t="s">
+        <v>186</v>
+      </c>
+      <c r="H23" t="s">
+        <v>185</v>
+      </c>
+      <c r="I23" t="s">
+        <v>187</v>
+      </c>
+      <c r="J23" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>181</v>
+      </c>
+      <c r="B24" s="6">
+        <v>0</v>
+      </c>
+      <c r="C24" s="6">
+        <v>12000</v>
+      </c>
+      <c r="D24" s="6">
+        <v>-2000</v>
+      </c>
+      <c r="E24" s="6">
+        <v>-5000</v>
+      </c>
+      <c r="F24" s="6">
+        <v>0</v>
+      </c>
+      <c r="G24" s="6">
+        <v>0</v>
+      </c>
+      <c r="H24" s="6">
+        <v>42000</v>
+      </c>
+      <c r="I24" s="6">
+        <v>18100</v>
+      </c>
+      <c r="J24" s="6">
+        <v>-29500</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>182</v>
+      </c>
+      <c r="B25" s="6">
+        <v>12000</v>
+      </c>
+      <c r="C25" s="6">
+        <v>0</v>
+      </c>
+      <c r="D25" s="6">
+        <v>-6000</v>
+      </c>
+      <c r="E25" s="6">
+        <v>-12000</v>
+      </c>
+      <c r="F25" s="6">
+        <v>10000</v>
+      </c>
+      <c r="G25" s="6">
+        <v>-30000</v>
+      </c>
+      <c r="H25" s="6">
+        <v>-47300</v>
+      </c>
+      <c r="I25" s="6">
+        <v>-4400</v>
+      </c>
+      <c r="J25" s="6">
+        <v>8600</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>183</v>
+      </c>
+      <c r="B26" s="6">
+        <v>-2000</v>
+      </c>
+      <c r="C26" s="6">
+        <v>-6000</v>
+      </c>
+      <c r="D26" s="6">
+        <v>0</v>
+      </c>
+      <c r="E26" s="6">
+        <v>-13000</v>
+      </c>
+      <c r="F26" s="6">
+        <v>0</v>
+      </c>
+      <c r="G26" s="6">
+        <v>-11300</v>
+      </c>
+      <c r="H26" s="6">
+        <v>6800</v>
+      </c>
+      <c r="I26" s="6">
+        <v>10400</v>
+      </c>
+      <c r="J26" s="6">
+        <v>-16000</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>192</v>
+      </c>
+      <c r="B27" s="6">
+        <v>-5000</v>
+      </c>
+      <c r="C27" s="6">
+        <v>-12000</v>
+      </c>
+      <c r="D27" s="6">
+        <v>-13000</v>
+      </c>
+      <c r="E27" s="6">
+        <v>0</v>
+      </c>
+      <c r="F27" s="6">
+        <v>-1600</v>
+      </c>
+      <c r="G27" s="6">
+        <v>6500</v>
+      </c>
+      <c r="H27" s="6">
+        <v>4000</v>
+      </c>
+      <c r="I27" s="6">
+        <v>21000</v>
+      </c>
+      <c r="J27" s="6">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>184</v>
+      </c>
+      <c r="B28" s="6">
+        <v>0</v>
+      </c>
+      <c r="C28" s="6">
+        <v>10000</v>
+      </c>
+      <c r="D28" s="6">
+        <v>0</v>
+      </c>
+      <c r="E28" s="6">
+        <v>-1600</v>
+      </c>
+      <c r="F28" s="6">
+        <v>0</v>
+      </c>
+      <c r="G28" s="6">
+        <v>12000</v>
+      </c>
+      <c r="H28" s="6">
+        <v>12000</v>
+      </c>
+      <c r="I28" s="6">
+        <v>11000</v>
+      </c>
+      <c r="J28" s="6">
+        <v>6400</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>186</v>
+      </c>
+      <c r="B29" s="6">
+        <v>0</v>
+      </c>
+      <c r="C29" s="6">
+        <v>-30000</v>
+      </c>
+      <c r="D29" s="6">
+        <v>-11300</v>
+      </c>
+      <c r="E29" s="6">
+        <v>6500</v>
+      </c>
+      <c r="F29" s="6">
+        <v>12000</v>
+      </c>
+      <c r="G29" s="6">
+        <v>0</v>
+      </c>
+      <c r="H29" s="6">
+        <v>18000</v>
+      </c>
+      <c r="I29" s="6">
+        <v>29000</v>
+      </c>
+      <c r="J29" s="6">
+        <v>-43500</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>185</v>
+      </c>
+      <c r="B30" s="6">
+        <v>42000</v>
+      </c>
+      <c r="C30" s="6">
+        <v>-47300</v>
+      </c>
+      <c r="D30" s="6">
+        <v>6800</v>
+      </c>
+      <c r="E30" s="6">
+        <v>4000</v>
+      </c>
+      <c r="F30" s="6">
+        <v>12000</v>
+      </c>
+      <c r="G30" s="6">
+        <v>18000</v>
+      </c>
+      <c r="H30" s="6">
+        <v>0</v>
+      </c>
+      <c r="I30" s="6">
+        <v>29000</v>
+      </c>
+      <c r="J30" s="6">
+        <v>-26000</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>187</v>
+      </c>
+      <c r="B31" s="6">
+        <v>18100</v>
+      </c>
+      <c r="C31" s="6">
+        <v>-4400</v>
+      </c>
+      <c r="D31" s="6">
+        <v>10400</v>
+      </c>
+      <c r="E31" s="6">
+        <v>21000</v>
+      </c>
+      <c r="F31" s="6">
+        <v>11000</v>
+      </c>
+      <c r="G31" s="6">
+        <v>29000</v>
+      </c>
+      <c r="H31" s="6">
+        <v>29000</v>
+      </c>
+      <c r="I31" s="6">
+        <v>0</v>
+      </c>
+      <c r="J31" s="6">
+        <v>9750</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>195</v>
+      </c>
+      <c r="B32" s="6">
+        <v>-29500</v>
+      </c>
+      <c r="C32" s="6">
+        <v>8600</v>
+      </c>
+      <c r="D32" s="6">
+        <v>-16000</v>
+      </c>
+      <c r="E32" s="6">
+        <v>3500</v>
+      </c>
+      <c r="F32" s="6">
+        <v>6400</v>
+      </c>
+      <c r="G32" s="6">
+        <v>-43500</v>
+      </c>
+      <c r="H32" s="6">
+        <v>-26000</v>
+      </c>
+      <c r="I32" s="6">
+        <v>9750</v>
+      </c>
+      <c r="J32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>34</v>
+      </c>
+      <c r="B34" t="s">
+        <v>181</v>
+      </c>
+      <c r="C34" t="s">
+        <v>182</v>
+      </c>
+      <c r="D34" t="s">
+        <v>183</v>
+      </c>
+      <c r="E34" t="s">
+        <v>192</v>
+      </c>
+      <c r="F34" t="s">
+        <v>184</v>
+      </c>
+      <c r="G34" t="s">
+        <v>186</v>
+      </c>
+      <c r="H34" t="s">
+        <v>185</v>
+      </c>
+      <c r="I34" t="s">
+        <v>187</v>
+      </c>
+      <c r="J34" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>181</v>
+      </c>
+      <c r="B35" s="6">
+        <v>0</v>
+      </c>
+      <c r="C35" s="6">
+        <v>0</v>
+      </c>
+      <c r="D35" s="6">
+        <v>0</v>
+      </c>
+      <c r="E35" s="6">
+        <v>0</v>
+      </c>
+      <c r="F35" s="6">
+        <v>0</v>
+      </c>
+      <c r="G35" s="6">
+        <v>0</v>
+      </c>
+      <c r="H35" s="6">
+        <v>0</v>
+      </c>
+      <c r="I35" s="6">
+        <v>0</v>
+      </c>
+      <c r="J35" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>182</v>
+      </c>
+      <c r="B36" s="6">
+        <v>0</v>
+      </c>
+      <c r="C36" s="6">
+        <v>0</v>
+      </c>
+      <c r="D36" s="6">
+        <v>0</v>
+      </c>
+      <c r="E36" s="6">
+        <v>0</v>
+      </c>
+      <c r="F36" s="6">
+        <v>0</v>
+      </c>
+      <c r="G36" s="6">
+        <v>0</v>
+      </c>
+      <c r="H36" s="6">
+        <v>0</v>
+      </c>
+      <c r="I36" s="6">
+        <v>0</v>
+      </c>
+      <c r="J36" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>183</v>
+      </c>
+      <c r="B37" s="6">
+        <v>0</v>
+      </c>
+      <c r="C37" s="6">
+        <v>0</v>
+      </c>
+      <c r="D37" s="6">
+        <v>0</v>
+      </c>
+      <c r="E37" s="6">
+        <v>0</v>
+      </c>
+      <c r="F37" s="6">
+        <v>0</v>
+      </c>
+      <c r="G37" s="6">
+        <v>0</v>
+      </c>
+      <c r="H37" s="6">
+        <v>0</v>
+      </c>
+      <c r="I37" s="6">
+        <v>0</v>
+      </c>
+      <c r="J37" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>192</v>
+      </c>
+      <c r="B38" s="6">
+        <v>0</v>
+      </c>
+      <c r="C38" s="6">
+        <v>0</v>
+      </c>
+      <c r="D38" s="6">
+        <v>0</v>
+      </c>
+      <c r="E38" s="6">
+        <v>0</v>
+      </c>
+      <c r="F38" s="6">
+        <v>0</v>
+      </c>
+      <c r="G38" s="6">
+        <v>0</v>
+      </c>
+      <c r="H38" s="6">
+        <v>0</v>
+      </c>
+      <c r="I38" s="6">
+        <v>0</v>
+      </c>
+      <c r="J38" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>184</v>
+      </c>
+      <c r="B39" s="6">
+        <v>0</v>
+      </c>
+      <c r="C39" s="6">
+        <v>0</v>
+      </c>
+      <c r="D39" s="6">
+        <v>0</v>
+      </c>
+      <c r="E39" s="6">
+        <v>0</v>
+      </c>
+      <c r="F39" s="6">
+        <v>0</v>
+      </c>
+      <c r="G39" s="6">
+        <v>0</v>
+      </c>
+      <c r="H39" s="6">
+        <v>0</v>
+      </c>
+      <c r="I39" s="6">
+        <v>0</v>
+      </c>
+      <c r="J39" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>186</v>
+      </c>
+      <c r="B40" s="6">
+        <v>0</v>
+      </c>
+      <c r="C40" s="6">
+        <v>0</v>
+      </c>
+      <c r="D40" s="6">
+        <v>0</v>
+      </c>
+      <c r="E40" s="6">
+        <v>0</v>
+      </c>
+      <c r="F40" s="6">
+        <v>0</v>
+      </c>
+      <c r="G40" s="6">
+        <v>0</v>
+      </c>
+      <c r="H40" s="6">
+        <v>0</v>
+      </c>
+      <c r="I40" s="6">
+        <v>0</v>
+      </c>
+      <c r="J40" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>185</v>
+      </c>
+      <c r="B41" s="6">
+        <v>0</v>
+      </c>
+      <c r="C41" s="6">
+        <v>0</v>
+      </c>
+      <c r="D41" s="6">
+        <v>0</v>
+      </c>
+      <c r="E41" s="6">
+        <v>0</v>
+      </c>
+      <c r="F41" s="6">
+        <v>0</v>
+      </c>
+      <c r="G41" s="6">
+        <v>0</v>
+      </c>
+      <c r="H41" s="6">
+        <v>0</v>
+      </c>
+      <c r="I41" s="6">
+        <v>0</v>
+      </c>
+      <c r="J41" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>187</v>
+      </c>
+      <c r="B42" s="6">
+        <v>0</v>
+      </c>
+      <c r="C42" s="6">
+        <v>0</v>
+      </c>
+      <c r="D42" s="6">
+        <v>0</v>
+      </c>
+      <c r="E42" s="6">
+        <v>0</v>
+      </c>
+      <c r="F42" s="6">
+        <v>0</v>
+      </c>
+      <c r="G42" s="6">
+        <v>0</v>
+      </c>
+      <c r="H42" s="6">
+        <v>0</v>
+      </c>
+      <c r="I42" s="6">
+        <v>0</v>
+      </c>
+      <c r="J42" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>195</v>
+      </c>
+      <c r="B43" s="6">
+        <v>0</v>
+      </c>
+      <c r="C43" s="6">
+        <v>0</v>
+      </c>
+      <c r="D43" s="6">
+        <v>0</v>
+      </c>
+      <c r="E43" s="6">
+        <v>0</v>
+      </c>
+      <c r="F43" s="6">
+        <v>0</v>
+      </c>
+      <c r="G43" s="6">
+        <v>0</v>
+      </c>
+      <c r="H43" s="6">
+        <v>0</v>
+      </c>
+      <c r="I43" s="6">
+        <v>0</v>
+      </c>
+      <c r="J43" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B44" s="6"/>
+      <c r="C44" s="6"/>
+      <c r="D44" s="6"/>
+      <c r="E44" s="6"/>
+      <c r="F44" s="6"/>
+      <c r="G44" s="6"/>
+      <c r="H44" s="6"/>
+      <c r="I44" s="6"/>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>35</v>
+      </c>
+      <c r="B45" t="s">
+        <v>181</v>
+      </c>
+      <c r="C45" t="s">
+        <v>182</v>
+      </c>
+      <c r="D45" t="s">
+        <v>183</v>
+      </c>
+      <c r="E45" t="s">
+        <v>192</v>
+      </c>
+      <c r="F45" t="s">
+        <v>184</v>
+      </c>
+      <c r="G45" t="s">
+        <v>186</v>
+      </c>
+      <c r="H45" t="s">
+        <v>185</v>
+      </c>
+      <c r="I45" t="s">
+        <v>187</v>
+      </c>
+      <c r="J45" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>181</v>
+      </c>
+      <c r="B46" s="6">
+        <v>0</v>
+      </c>
+      <c r="C46" s="6">
+        <v>-400</v>
+      </c>
+      <c r="D46" s="6">
+        <v>-500</v>
+      </c>
+      <c r="E46" s="6">
+        <v>0</v>
+      </c>
+      <c r="F46" s="6">
+        <v>0</v>
+      </c>
+      <c r="G46" s="6">
+        <v>0</v>
+      </c>
+      <c r="H46" s="6">
+        <v>1000</v>
+      </c>
+      <c r="I46" s="6">
+        <v>-680</v>
+      </c>
+      <c r="J46" s="6">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>182</v>
+      </c>
+      <c r="B47" s="6">
+        <v>-400</v>
+      </c>
+      <c r="C47" s="6">
+        <v>0</v>
+      </c>
+      <c r="D47" s="6">
+        <v>3000</v>
+      </c>
+      <c r="E47" s="6">
+        <v>0</v>
+      </c>
+      <c r="F47" s="6">
+        <v>0</v>
+      </c>
+      <c r="G47" s="6">
+        <v>800</v>
+      </c>
+      <c r="H47" s="6">
+        <v>300</v>
+      </c>
+      <c r="I47" s="6">
+        <v>-170</v>
+      </c>
+      <c r="J47" s="6">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>183</v>
+      </c>
+      <c r="B48" s="6">
+        <v>-500</v>
+      </c>
+      <c r="C48" s="6">
+        <v>3000</v>
+      </c>
+      <c r="D48" s="6">
+        <v>0</v>
+      </c>
+      <c r="E48" s="6">
+        <v>0</v>
+      </c>
+      <c r="F48" s="6">
+        <v>0</v>
+      </c>
+      <c r="G48" s="6">
+        <v>0</v>
+      </c>
+      <c r="H48" s="6">
+        <v>0</v>
+      </c>
+      <c r="I48" s="6">
+        <v>-390</v>
+      </c>
+      <c r="J48" s="6">
+        <v>-250</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>192</v>
+      </c>
+      <c r="B49" s="6">
+        <v>0</v>
+      </c>
+      <c r="C49" s="6">
+        <v>0</v>
+      </c>
+      <c r="D49" s="6">
+        <v>0</v>
+      </c>
+      <c r="E49" s="6">
+        <v>0</v>
+      </c>
+      <c r="F49" s="6">
+        <v>0</v>
+      </c>
+      <c r="G49" s="6">
+        <v>0</v>
+      </c>
+      <c r="H49" s="6">
+        <v>0</v>
+      </c>
+      <c r="I49" s="6">
+        <v>0</v>
+      </c>
+      <c r="J49" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>184</v>
+      </c>
+      <c r="B50" s="6">
+        <v>0</v>
+      </c>
+      <c r="C50" s="6">
+        <v>0</v>
+      </c>
+      <c r="D50" s="6">
+        <v>0</v>
+      </c>
+      <c r="E50" s="6">
+        <v>0</v>
+      </c>
+      <c r="F50" s="6">
+        <v>0</v>
+      </c>
+      <c r="G50" s="6">
+        <v>0</v>
+      </c>
+      <c r="H50" s="6">
+        <v>0</v>
+      </c>
+      <c r="I50" s="6">
+        <v>-500</v>
+      </c>
+      <c r="J50" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>186</v>
+      </c>
+      <c r="B51" s="6">
+        <v>0</v>
+      </c>
+      <c r="C51" s="6">
+        <v>800</v>
+      </c>
+      <c r="D51" s="6">
+        <v>0</v>
+      </c>
+      <c r="E51" s="6">
+        <v>0</v>
+      </c>
+      <c r="F51" s="6">
+        <v>0</v>
+      </c>
+      <c r="G51" s="6">
+        <v>0</v>
+      </c>
+      <c r="H51" s="6">
+        <v>0</v>
+      </c>
+      <c r="I51" s="6">
+        <v>0</v>
+      </c>
+      <c r="J51" s="6">
+        <v>-950</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>185</v>
+      </c>
+      <c r="B52" s="6">
+        <v>1000</v>
+      </c>
+      <c r="C52" s="6">
+        <v>300</v>
+      </c>
+      <c r="D52" s="6">
+        <v>0</v>
+      </c>
+      <c r="E52" s="6">
+        <v>0</v>
+      </c>
+      <c r="F52" s="6">
+        <v>0</v>
+      </c>
+      <c r="G52" s="6">
+        <v>0</v>
+      </c>
+      <c r="H52" s="6">
+        <v>0</v>
+      </c>
+      <c r="I52" s="6">
+        <v>-500</v>
+      </c>
+      <c r="J52" s="6">
+        <v>-600</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>187</v>
+      </c>
+      <c r="B53" s="6">
+        <v>-680</v>
+      </c>
+      <c r="C53" s="6">
+        <v>-170</v>
+      </c>
+      <c r="D53" s="6">
+        <v>-390</v>
+      </c>
+      <c r="E53" s="6">
+        <v>0</v>
+      </c>
+      <c r="F53" s="6">
+        <v>-500</v>
+      </c>
+      <c r="G53" s="6">
+        <v>0</v>
+      </c>
+      <c r="H53" s="6">
+        <v>-500</v>
+      </c>
+      <c r="I53" s="6">
+        <v>0</v>
+      </c>
+      <c r="J53" s="6">
+        <v>-500</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>195</v>
+      </c>
+      <c r="B54" s="6">
+        <v>-100</v>
+      </c>
+      <c r="C54" s="6">
+        <v>400</v>
+      </c>
+      <c r="D54" s="6">
+        <v>-250</v>
+      </c>
+      <c r="E54" s="6">
+        <v>0</v>
+      </c>
+      <c r="F54" s="6">
+        <v>0</v>
+      </c>
+      <c r="G54" s="6">
+        <v>-950</v>
+      </c>
+      <c r="H54" s="6">
+        <v>-600</v>
+      </c>
+      <c r="I54" s="6">
+        <v>-500</v>
+      </c>
+      <c r="J54" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B55" s="6"/>
+      <c r="C55" s="6"/>
+      <c r="D55" s="6"/>
+      <c r="E55" s="6"/>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>36</v>
+      </c>
+      <c r="B56" t="s">
+        <v>181</v>
+      </c>
+      <c r="C56" t="s">
+        <v>182</v>
+      </c>
+      <c r="D56" t="s">
+        <v>183</v>
+      </c>
+      <c r="E56" t="s">
+        <v>192</v>
+      </c>
+      <c r="F56" t="s">
+        <v>184</v>
+      </c>
+      <c r="G56" t="s">
+        <v>186</v>
+      </c>
+      <c r="H56" t="s">
+        <v>185</v>
+      </c>
+      <c r="I56" t="s">
+        <v>187</v>
+      </c>
+      <c r="J56" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>37</v>
+      </c>
+      <c r="B57">
+        <v>1</v>
+      </c>
+      <c r="C57">
+        <v>1</v>
+      </c>
+      <c r="D57">
+        <v>1</v>
+      </c>
+      <c r="E57">
+        <v>1</v>
+      </c>
+      <c r="F57">
+        <v>1</v>
+      </c>
+      <c r="G57">
+        <v>1</v>
+      </c>
+      <c r="H57">
+        <v>1</v>
+      </c>
+      <c r="I57">
+        <v>1</v>
+      </c>
+      <c r="J57">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>38</v>
+      </c>
+      <c r="B58">
+        <v>0</v>
+      </c>
+      <c r="C58">
+        <v>0</v>
+      </c>
+      <c r="D58">
+        <v>0</v>
+      </c>
+      <c r="E58">
+        <v>0</v>
+      </c>
+      <c r="F58">
+        <v>0</v>
+      </c>
+      <c r="G58">
+        <v>0</v>
+      </c>
+      <c r="H58">
+        <v>0</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>39</v>
+      </c>
+      <c r="B59">
+        <v>0</v>
+      </c>
+      <c r="C59">
+        <v>0</v>
+      </c>
+      <c r="D59">
+        <v>0</v>
+      </c>
+      <c r="E59">
+        <v>0</v>
+      </c>
+      <c r="F59">
+        <v>0</v>
+      </c>
+      <c r="G59">
+        <v>0</v>
+      </c>
+      <c r="H59">
+        <v>0</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{956F8C11-B9B7-488A-A996-46E9938D33E3}">
+  <dimension ref="A1:M55"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="12.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D3" t="s">
+        <v>73</v>
+      </c>
+      <c r="E3" t="s">
+        <v>73</v>
+      </c>
+      <c r="F3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J3" t="s">
+        <v>6</v>
+      </c>
+      <c r="K3" t="s">
+        <v>6</v>
+      </c>
+      <c r="L3" t="s">
+        <v>130</v>
+      </c>
+      <c r="M3" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I4" t="s">
+        <v>10</v>
+      </c>
+      <c r="J4" t="s">
+        <v>18</v>
+      </c>
+      <c r="K4" t="s">
+        <v>14</v>
+      </c>
+      <c r="L4" t="s">
+        <v>18</v>
+      </c>
+      <c r="M4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>66</v>
+      </c>
+      <c r="B6" s="1">
+        <v>1</v>
+      </c>
+      <c r="C6" s="1">
+        <v>0</v>
+      </c>
+      <c r="D6" s="1">
+        <v>0</v>
+      </c>
+      <c r="E6" s="1">
+        <v>0</v>
+      </c>
+      <c r="F6" s="1">
+        <v>0</v>
+      </c>
+      <c r="G6" s="1">
+        <v>0</v>
+      </c>
+      <c r="H6" s="1">
+        <v>1</v>
+      </c>
+      <c r="I6" s="1">
+        <v>0</v>
+      </c>
+      <c r="J6" s="1">
+        <v>1</v>
+      </c>
+      <c r="K6" s="1">
+        <v>0</v>
+      </c>
+      <c r="L6" s="1">
+        <v>1</v>
+      </c>
+      <c r="M6" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>200</v>
+      </c>
+      <c r="B7" s="1">
+        <v>1</v>
+      </c>
+      <c r="C7" s="1">
+        <v>0</v>
+      </c>
+      <c r="D7" s="1">
+        <v>0</v>
+      </c>
+      <c r="E7" s="1">
+        <v>0</v>
+      </c>
+      <c r="F7" s="1">
+        <v>1</v>
+      </c>
+      <c r="G7" s="1">
+        <v>0</v>
+      </c>
+      <c r="H7" s="1">
+        <v>0</v>
+      </c>
+      <c r="I7" s="1">
+        <v>0</v>
+      </c>
+      <c r="J7" s="1">
+        <v>1</v>
+      </c>
+      <c r="K7" s="1">
+        <v>0</v>
+      </c>
+      <c r="L7" s="1">
+        <v>1</v>
+      </c>
+      <c r="M7" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>201</v>
+      </c>
+      <c r="B8" s="1">
+        <v>0</v>
+      </c>
+      <c r="C8" s="1">
+        <v>1</v>
+      </c>
+      <c r="D8" s="1">
+        <v>0</v>
+      </c>
+      <c r="E8" s="1">
+        <v>0</v>
+      </c>
+      <c r="F8" s="1">
+        <v>0</v>
+      </c>
+      <c r="G8" s="1">
+        <v>1</v>
+      </c>
+      <c r="H8" s="1">
+        <v>0</v>
+      </c>
+      <c r="I8" s="1">
+        <v>0</v>
+      </c>
+      <c r="J8" s="1">
+        <v>1</v>
+      </c>
+      <c r="K8" s="1">
+        <v>0</v>
+      </c>
+      <c r="L8" s="1">
+        <v>1</v>
+      </c>
+      <c r="M8" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>202</v>
+      </c>
+      <c r="B9" s="1">
+        <v>0</v>
+      </c>
+      <c r="C9" s="1">
+        <v>0</v>
+      </c>
+      <c r="D9" s="1">
+        <v>1</v>
+      </c>
+      <c r="E9" s="1">
+        <v>0</v>
+      </c>
+      <c r="F9" s="1">
+        <v>0</v>
+      </c>
+      <c r="G9" s="1">
+        <v>0</v>
+      </c>
+      <c r="H9" s="1">
+        <v>0</v>
+      </c>
+      <c r="I9" s="1">
+        <v>1</v>
+      </c>
+      <c r="J9" s="1">
+        <v>1</v>
+      </c>
+      <c r="K9" s="1">
+        <v>0</v>
+      </c>
+      <c r="L9" s="1">
+        <v>1</v>
+      </c>
+      <c r="M9" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>212</v>
+      </c>
+      <c r="B10" s="1">
+        <v>0</v>
+      </c>
+      <c r="C10" s="1">
+        <v>0</v>
+      </c>
+      <c r="D10" s="1">
+        <v>0</v>
+      </c>
+      <c r="E10" s="1">
+        <v>1</v>
+      </c>
+      <c r="F10" s="1">
+        <v>0</v>
+      </c>
+      <c r="G10" s="1">
+        <v>0</v>
+      </c>
+      <c r="H10" s="1">
+        <v>0</v>
+      </c>
+      <c r="I10" s="1">
+        <v>1</v>
+      </c>
+      <c r="J10" s="1">
+        <v>1</v>
+      </c>
+      <c r="K10" s="1">
+        <v>0</v>
+      </c>
+      <c r="L10" s="1">
+        <v>1</v>
+      </c>
+      <c r="M10" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>203</v>
+      </c>
+      <c r="B11" s="1">
+        <v>0</v>
+      </c>
+      <c r="C11" s="1">
+        <v>0</v>
+      </c>
+      <c r="D11" s="1">
+        <v>1</v>
+      </c>
+      <c r="E11" s="1">
+        <v>0</v>
+      </c>
+      <c r="F11" s="1">
+        <v>0</v>
+      </c>
+      <c r="G11" s="1">
+        <v>0</v>
+      </c>
+      <c r="H11" s="1">
+        <v>1</v>
+      </c>
+      <c r="I11" s="1">
+        <v>0</v>
+      </c>
+      <c r="J11" s="1">
+        <v>1</v>
+      </c>
+      <c r="K11" s="1">
+        <v>0</v>
+      </c>
+      <c r="L11" s="1">
+        <v>0</v>
+      </c>
+      <c r="M11" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>204</v>
+      </c>
+      <c r="B12" s="1">
+        <v>0</v>
+      </c>
+      <c r="C12" s="1">
+        <v>0</v>
+      </c>
+      <c r="D12" s="1">
+        <v>1</v>
+      </c>
+      <c r="E12" s="1">
+        <v>0</v>
+      </c>
+      <c r="F12" s="1">
+        <v>0</v>
+      </c>
+      <c r="G12" s="1">
+        <v>0</v>
+      </c>
+      <c r="H12" s="1">
+        <v>1</v>
+      </c>
+      <c r="I12" s="1">
+        <v>0</v>
+      </c>
+      <c r="J12" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="K12" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="L12" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="M12" s="1">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>205</v>
+      </c>
+      <c r="B13" s="1">
+        <v>1</v>
+      </c>
+      <c r="C13" s="1">
+        <v>0</v>
+      </c>
+      <c r="D13" s="1">
+        <v>0</v>
+      </c>
+      <c r="E13" s="1">
+        <v>0</v>
+      </c>
+      <c r="F13" s="1">
+        <v>0</v>
+      </c>
+      <c r="G13" s="1">
+        <v>1</v>
+      </c>
+      <c r="H13" s="1">
+        <v>0</v>
+      </c>
+      <c r="I13" s="1">
+        <v>0</v>
+      </c>
+      <c r="J13" s="1">
+        <v>1</v>
+      </c>
+      <c r="K13" s="1">
+        <v>0</v>
+      </c>
+      <c r="L13" s="1">
+        <v>1</v>
+      </c>
+      <c r="M13" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
+      <c r="I14" s="1"/>
+      <c r="J14" s="1"/>
+      <c r="K14" s="1"/>
+      <c r="L14" s="1"/>
+      <c r="M14" s="1"/>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" s="1">
+        <v>1</v>
+      </c>
+      <c r="C15" s="1">
+        <v>1</v>
+      </c>
+      <c r="D15" s="1">
+        <v>1</v>
+      </c>
+      <c r="E15" s="1">
+        <v>1</v>
+      </c>
+      <c r="F15" s="1">
+        <v>1</v>
+      </c>
+      <c r="G15" s="1">
+        <v>1</v>
+      </c>
+      <c r="H15" s="1">
+        <v>1</v>
+      </c>
+      <c r="I15" s="1">
+        <v>1</v>
+      </c>
+      <c r="J15" s="6">
+        <v>0.25</v>
+      </c>
+      <c r="K15" s="6">
+        <v>0.25</v>
+      </c>
+      <c r="L15" s="6">
+        <v>0.25</v>
+      </c>
+      <c r="M15" s="6">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>22</v>
+      </c>
+      <c r="B17" s="1">
+        <v>0</v>
+      </c>
+      <c r="C17" s="1">
+        <v>0</v>
+      </c>
+      <c r="D17" s="1">
+        <v>0</v>
+      </c>
+      <c r="E17" s="1">
+        <v>0</v>
+      </c>
+      <c r="F17" s="1">
+        <v>0</v>
+      </c>
+      <c r="G17" s="1">
+        <v>0</v>
+      </c>
+      <c r="H17" s="1">
+        <v>0</v>
+      </c>
+      <c r="I17" s="1">
+        <v>0</v>
+      </c>
+      <c r="J17" s="1">
+        <v>0</v>
+      </c>
+      <c r="K17" s="1">
+        <v>0</v>
+      </c>
+      <c r="L17" s="1">
+        <v>0</v>
+      </c>
+      <c r="M17" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>23</v>
+      </c>
+      <c r="B18" s="1">
+        <v>1</v>
+      </c>
+      <c r="C18" s="1">
+        <v>1</v>
+      </c>
+      <c r="D18" s="1">
+        <v>1</v>
+      </c>
+      <c r="E18" s="1">
+        <v>1</v>
+      </c>
+      <c r="F18" s="1">
+        <v>1</v>
+      </c>
+      <c r="G18" s="1">
+        <v>1</v>
+      </c>
+      <c r="H18" s="1">
+        <v>1</v>
+      </c>
+      <c r="I18" s="1">
+        <v>1</v>
+      </c>
+      <c r="J18" s="1">
+        <v>1</v>
+      </c>
+      <c r="K18" s="1">
+        <v>1</v>
+      </c>
+      <c r="L18" s="1">
+        <v>1</v>
+      </c>
+      <c r="M18" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>24</v>
+      </c>
+      <c r="B19" s="2">
+        <v>6.7000000000000004E-2</v>
+      </c>
+      <c r="C19" s="2">
+        <v>6.7000000000000004E-2</v>
+      </c>
+      <c r="D19" s="2">
+        <v>6.7000000000000004E-2</v>
+      </c>
+      <c r="E19" s="2">
+        <v>6.7000000000000004E-2</v>
+      </c>
+      <c r="F19" s="2">
+        <v>6.7000000000000004E-2</v>
+      </c>
+      <c r="G19" s="2">
+        <v>6.7000000000000004E-2</v>
+      </c>
+      <c r="H19" s="2">
+        <v>6.7000000000000004E-2</v>
+      </c>
+      <c r="I19" s="2">
+        <v>6.7000000000000004E-2</v>
+      </c>
+      <c r="J19" s="2">
+        <v>6.7000000000000004E-2</v>
+      </c>
+      <c r="K19" s="2">
+        <v>6.7000000000000004E-2</v>
+      </c>
+      <c r="L19" s="2">
+        <v>6.7000000000000004E-2</v>
+      </c>
+      <c r="M19" s="2">
+        <v>6.7000000000000004E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>25</v>
+      </c>
+      <c r="B20" s="1">
+        <v>0</v>
+      </c>
+      <c r="C20" s="1">
+        <v>0</v>
+      </c>
+      <c r="D20" s="1">
+        <v>0</v>
+      </c>
+      <c r="E20" s="1">
+        <v>0</v>
+      </c>
+      <c r="F20" s="1">
+        <v>0</v>
+      </c>
+      <c r="G20" s="1">
+        <v>0</v>
+      </c>
+      <c r="H20" s="1">
+        <v>0</v>
+      </c>
+      <c r="I20" s="1">
+        <v>0</v>
+      </c>
+      <c r="J20" s="1">
+        <v>0</v>
+      </c>
+      <c r="K20" s="1">
+        <v>0</v>
+      </c>
+      <c r="L20" s="1">
+        <v>0</v>
+      </c>
+      <c r="M20" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>26</v>
+      </c>
+      <c r="B22" t="s">
+        <v>60</v>
+      </c>
+      <c r="C22" t="s">
+        <v>206</v>
+      </c>
+      <c r="D22" t="s">
+        <v>207</v>
+      </c>
+      <c r="E22" t="s">
+        <v>208</v>
+      </c>
+      <c r="F22" t="s">
+        <v>72</v>
+      </c>
+      <c r="G22" t="s">
+        <v>209</v>
+      </c>
+      <c r="H22" t="s">
+        <v>210</v>
+      </c>
+      <c r="I22" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>66</v>
+      </c>
+      <c r="B23" s="3">
+        <v>0</v>
+      </c>
+      <c r="C23" s="3">
+        <v>29800</v>
+      </c>
+      <c r="D23" s="3">
+        <v>25800</v>
+      </c>
+      <c r="E23" s="3">
+        <v>26000</v>
+      </c>
+      <c r="F23" s="3">
+        <v>21000</v>
+      </c>
+      <c r="G23" s="3">
+        <v>12300</v>
+      </c>
+      <c r="H23" s="3">
+        <v>12300</v>
+      </c>
+      <c r="I23" s="3">
+        <v>20600</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>200</v>
+      </c>
+      <c r="B24" s="3">
+        <v>29800</v>
+      </c>
+      <c r="C24" s="3">
+        <v>0</v>
+      </c>
+      <c r="D24" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E24" s="3">
+        <v>50000</v>
+      </c>
+      <c r="F24" s="3">
+        <v>62000</v>
+      </c>
+      <c r="G24" s="3">
+        <v>45700</v>
+      </c>
+      <c r="H24" s="3">
+        <v>45700</v>
+      </c>
+      <c r="I24" s="3">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>201</v>
+      </c>
+      <c r="B25" s="3">
+        <v>25800</v>
+      </c>
+      <c r="C25" s="3">
+        <v>2300</v>
+      </c>
+      <c r="D25" s="3">
+        <v>0</v>
+      </c>
+      <c r="E25" s="3">
+        <v>60000</v>
+      </c>
+      <c r="F25" s="3">
+        <v>58000</v>
+      </c>
+      <c r="G25" s="3">
+        <v>48000</v>
+      </c>
+      <c r="H25" s="3">
+        <v>48000</v>
+      </c>
+      <c r="I25" s="3">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>202</v>
+      </c>
+      <c r="B26" s="3">
+        <v>26000</v>
+      </c>
+      <c r="C26" s="3">
+        <v>50000</v>
+      </c>
+      <c r="D26" s="3">
+        <v>60000</v>
+      </c>
+      <c r="E26" s="3">
+        <v>0</v>
+      </c>
+      <c r="F26" s="3">
+        <v>5000</v>
+      </c>
+      <c r="G26" s="3">
+        <v>40000</v>
+      </c>
+      <c r="H26" s="3">
+        <v>40000</v>
+      </c>
+      <c r="I26" s="3">
+        <v>40000</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>68</v>
+      </c>
+      <c r="B27" s="3">
+        <v>21000</v>
+      </c>
+      <c r="C27" s="3">
+        <v>62000</v>
+      </c>
+      <c r="D27" s="3">
+        <v>58000</v>
+      </c>
+      <c r="E27" s="3">
+        <v>5000</v>
+      </c>
+      <c r="F27" s="3">
+        <v>0</v>
+      </c>
+      <c r="G27" s="3">
+        <v>35000</v>
+      </c>
+      <c r="H27" s="3">
+        <v>35000</v>
+      </c>
+      <c r="I27" s="3">
+        <v>60000</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>203</v>
+      </c>
+      <c r="B28" s="3">
+        <v>12300</v>
+      </c>
+      <c r="C28" s="3">
+        <v>45700</v>
+      </c>
+      <c r="D28" s="3">
+        <v>48000</v>
+      </c>
+      <c r="E28" s="3">
+        <v>40000</v>
+      </c>
+      <c r="F28" s="3">
+        <v>35000</v>
+      </c>
+      <c r="G28" s="3">
+        <v>0</v>
+      </c>
+      <c r="H28" s="3">
+        <v>3800</v>
+      </c>
+      <c r="I28" s="3">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>204</v>
+      </c>
+      <c r="B29" s="3">
+        <v>12300</v>
+      </c>
+      <c r="C29" s="3">
+        <v>45700</v>
+      </c>
+      <c r="D29" s="3">
+        <v>48000</v>
+      </c>
+      <c r="E29" s="3">
+        <v>40000</v>
+      </c>
+      <c r="F29" s="3">
+        <v>35000</v>
+      </c>
+      <c r="G29" s="3">
+        <v>3800</v>
+      </c>
+      <c r="H29" s="3">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>205</v>
+      </c>
+      <c r="B30" s="3">
+        <v>20600</v>
+      </c>
+      <c r="C30" s="3">
+        <v>4000</v>
+      </c>
+      <c r="D30" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E30" s="3">
+        <v>40000</v>
+      </c>
+      <c r="F30" s="3">
+        <v>60000</v>
+      </c>
+      <c r="G30" s="3">
+        <v>50000</v>
+      </c>
+      <c r="H30" s="3">
+        <v>50000</v>
+      </c>
+      <c r="I30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>34</v>
+      </c>
+      <c r="B32" t="s">
+        <v>60</v>
+      </c>
+      <c r="C32" t="s">
+        <v>206</v>
+      </c>
+      <c r="D32" t="s">
+        <v>207</v>
+      </c>
+      <c r="E32" t="s">
+        <v>208</v>
+      </c>
+      <c r="F32" t="s">
+        <v>72</v>
+      </c>
+      <c r="G32" t="s">
+        <v>209</v>
+      </c>
+      <c r="H32" t="s">
+        <v>210</v>
+      </c>
+      <c r="I32" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>66</v>
+      </c>
+      <c r="B33" s="3">
+        <v>0</v>
+      </c>
+      <c r="C33" s="3">
+        <v>0</v>
+      </c>
+      <c r="D33" s="3">
+        <v>0</v>
+      </c>
+      <c r="E33" s="3">
+        <v>0</v>
+      </c>
+      <c r="F33" s="3">
+        <v>0</v>
+      </c>
+      <c r="G33" s="3">
+        <v>0</v>
+      </c>
+      <c r="H33" s="3">
+        <v>0</v>
+      </c>
+      <c r="I33" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>200</v>
+      </c>
+      <c r="B34" s="3">
+        <v>0</v>
+      </c>
+      <c r="C34" s="3">
+        <v>0</v>
+      </c>
+      <c r="D34" s="3">
+        <v>0</v>
+      </c>
+      <c r="E34" s="3">
+        <v>0</v>
+      </c>
+      <c r="F34" s="3">
+        <v>0</v>
+      </c>
+      <c r="G34" s="3">
+        <v>0</v>
+      </c>
+      <c r="H34" s="3">
+        <v>0</v>
+      </c>
+      <c r="I34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>201</v>
+      </c>
+      <c r="B35" s="3">
+        <v>0</v>
+      </c>
+      <c r="C35" s="3">
+        <v>0</v>
+      </c>
+      <c r="D35" s="3">
+        <v>0</v>
+      </c>
+      <c r="E35" s="3">
+        <v>0</v>
+      </c>
+      <c r="F35" s="3">
+        <v>0</v>
+      </c>
+      <c r="G35" s="3">
+        <v>0</v>
+      </c>
+      <c r="H35" s="3">
+        <v>0</v>
+      </c>
+      <c r="I35" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>202</v>
+      </c>
+      <c r="B36" s="3">
+        <v>0</v>
+      </c>
+      <c r="C36" s="3">
+        <v>0</v>
+      </c>
+      <c r="D36" s="3">
+        <v>0</v>
+      </c>
+      <c r="E36" s="3">
+        <v>0</v>
+      </c>
+      <c r="F36" s="3">
+        <v>0</v>
+      </c>
+      <c r="G36" s="3">
+        <v>0</v>
+      </c>
+      <c r="H36" s="3">
+        <v>0</v>
+      </c>
+      <c r="I36" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>68</v>
+      </c>
+      <c r="B37" s="3">
+        <v>0</v>
+      </c>
+      <c r="C37" s="3">
+        <v>0</v>
+      </c>
+      <c r="D37" s="3">
+        <v>0</v>
+      </c>
+      <c r="E37" s="3">
+        <v>0</v>
+      </c>
+      <c r="F37" s="3">
+        <v>0</v>
+      </c>
+      <c r="G37" s="3">
+        <v>0</v>
+      </c>
+      <c r="H37" s="3">
+        <v>0</v>
+      </c>
+      <c r="I37" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>203</v>
+      </c>
+      <c r="B38" s="3">
+        <v>0</v>
+      </c>
+      <c r="C38" s="3">
+        <v>0</v>
+      </c>
+      <c r="D38" s="3">
+        <v>0</v>
+      </c>
+      <c r="E38" s="3">
+        <v>0</v>
+      </c>
+      <c r="F38" s="3">
+        <v>0</v>
+      </c>
+      <c r="G38" s="3">
+        <v>0</v>
+      </c>
+      <c r="H38" s="3">
+        <v>0</v>
+      </c>
+      <c r="I38" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>204</v>
+      </c>
+      <c r="B39" s="3">
+        <v>0</v>
+      </c>
+      <c r="C39" s="3">
+        <v>0</v>
+      </c>
+      <c r="D39" s="3">
+        <v>0</v>
+      </c>
+      <c r="E39" s="3">
+        <v>0</v>
+      </c>
+      <c r="F39" s="3">
+        <v>0</v>
+      </c>
+      <c r="G39" s="3">
+        <v>0</v>
+      </c>
+      <c r="H39" s="3">
+        <v>0</v>
+      </c>
+      <c r="I39" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>205</v>
+      </c>
+      <c r="B40" s="3">
+        <v>0</v>
+      </c>
+      <c r="C40" s="3">
+        <v>0</v>
+      </c>
+      <c r="D40" s="3">
+        <v>0</v>
+      </c>
+      <c r="E40" s="3">
+        <v>0</v>
+      </c>
+      <c r="F40" s="3">
+        <v>0</v>
+      </c>
+      <c r="G40" s="3">
+        <v>0</v>
+      </c>
+      <c r="H40" s="3">
+        <v>0</v>
+      </c>
+      <c r="I40" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>35</v>
+      </c>
+      <c r="B42" t="s">
+        <v>60</v>
+      </c>
+      <c r="C42" t="s">
+        <v>206</v>
+      </c>
+      <c r="D42" t="s">
+        <v>207</v>
+      </c>
+      <c r="E42" t="s">
+        <v>208</v>
+      </c>
+      <c r="F42" t="s">
+        <v>72</v>
+      </c>
+      <c r="G42" t="s">
+        <v>209</v>
+      </c>
+      <c r="H42" t="s">
+        <v>210</v>
+      </c>
+      <c r="I42" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>66</v>
+      </c>
+      <c r="B43" s="3">
+        <v>0</v>
+      </c>
+      <c r="C43" s="6">
+        <v>-30</v>
+      </c>
+      <c r="D43" s="6">
+        <v>-30</v>
+      </c>
+      <c r="E43" s="6">
+        <v>0</v>
+      </c>
+      <c r="F43" s="6">
+        <v>0</v>
+      </c>
+      <c r="G43" s="6">
+        <v>-10</v>
+      </c>
+      <c r="H43" s="6">
+        <v>-10</v>
+      </c>
+      <c r="I43" s="6">
+        <v>-30</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>200</v>
+      </c>
+      <c r="B44" s="6">
+        <v>-30</v>
+      </c>
+      <c r="C44" s="3">
+        <v>0</v>
+      </c>
+      <c r="D44" s="6">
+        <v>0</v>
+      </c>
+      <c r="E44" s="6">
+        <v>0</v>
+      </c>
+      <c r="F44" s="6">
+        <v>0</v>
+      </c>
+      <c r="G44" s="6">
+        <v>-290</v>
+      </c>
+      <c r="H44" s="6">
+        <v>-290</v>
+      </c>
+      <c r="I44" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>201</v>
+      </c>
+      <c r="B45" s="6">
+        <v>-30</v>
+      </c>
+      <c r="C45" s="6">
+        <v>0</v>
+      </c>
+      <c r="D45" s="3">
+        <v>0</v>
+      </c>
+      <c r="E45" s="6">
+        <v>0</v>
+      </c>
+      <c r="F45" s="6">
+        <v>0</v>
+      </c>
+      <c r="G45" s="6">
+        <v>0</v>
+      </c>
+      <c r="H45" s="6">
+        <v>0</v>
+      </c>
+      <c r="I45" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>202</v>
+      </c>
+      <c r="B46" s="6">
+        <v>0</v>
+      </c>
+      <c r="C46" s="6">
+        <v>0</v>
+      </c>
+      <c r="D46" s="6">
+        <v>0</v>
+      </c>
+      <c r="E46" s="3">
+        <v>0</v>
+      </c>
+      <c r="F46" s="6">
+        <v>0</v>
+      </c>
+      <c r="G46" s="6">
+        <v>0</v>
+      </c>
+      <c r="H46" s="6">
+        <v>0</v>
+      </c>
+      <c r="I46" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>68</v>
+      </c>
+      <c r="B47" s="6">
+        <v>0</v>
+      </c>
+      <c r="C47" s="6">
+        <v>0</v>
+      </c>
+      <c r="D47" s="6">
+        <v>0</v>
+      </c>
+      <c r="E47" s="6">
+        <v>0</v>
+      </c>
+      <c r="F47" s="3">
+        <v>0</v>
+      </c>
+      <c r="G47" s="6">
+        <v>0</v>
+      </c>
+      <c r="H47" s="6">
+        <v>0</v>
+      </c>
+      <c r="I47" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>203</v>
+      </c>
+      <c r="B48" s="6">
+        <v>-10</v>
+      </c>
+      <c r="C48" s="6">
+        <v>-290</v>
+      </c>
+      <c r="D48" s="6">
+        <v>0</v>
+      </c>
+      <c r="E48" s="6">
+        <v>0</v>
+      </c>
+      <c r="F48" s="6">
+        <v>0</v>
+      </c>
+      <c r="G48" s="3">
+        <v>0</v>
+      </c>
+      <c r="H48" s="6">
+        <v>10</v>
+      </c>
+      <c r="I48" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>204</v>
+      </c>
+      <c r="B49" s="6">
+        <v>-10</v>
+      </c>
+      <c r="C49" s="6">
+        <v>-290</v>
+      </c>
+      <c r="D49" s="6">
+        <v>0</v>
+      </c>
+      <c r="E49" s="6">
+        <v>0</v>
+      </c>
+      <c r="F49" s="6">
+        <v>0</v>
+      </c>
+      <c r="G49" s="6">
+        <v>10</v>
+      </c>
+      <c r="H49" s="3">
+        <v>0</v>
+      </c>
+      <c r="I49" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>205</v>
+      </c>
+      <c r="B50" s="6">
+        <v>-30</v>
+      </c>
+      <c r="C50" s="6">
+        <v>0</v>
+      </c>
+      <c r="D50" s="6">
+        <v>0</v>
+      </c>
+      <c r="E50" s="6">
+        <v>0</v>
+      </c>
+      <c r="F50" s="6">
+        <v>0</v>
+      </c>
+      <c r="G50" s="6">
+        <v>0</v>
+      </c>
+      <c r="H50" s="6">
+        <v>0</v>
+      </c>
+      <c r="I50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>36</v>
+      </c>
+      <c r="B52" t="s">
+        <v>60</v>
+      </c>
+      <c r="C52" t="s">
+        <v>206</v>
+      </c>
+      <c r="D52" t="s">
+        <v>207</v>
+      </c>
+      <c r="E52" t="s">
+        <v>208</v>
+      </c>
+      <c r="F52" t="s">
+        <v>72</v>
+      </c>
+      <c r="G52" t="s">
+        <v>209</v>
+      </c>
+      <c r="H52" t="s">
+        <v>210</v>
+      </c>
+      <c r="I52" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>37</v>
+      </c>
+      <c r="B53">
+        <v>1.2</v>
+      </c>
+      <c r="C53">
+        <v>1</v>
+      </c>
+      <c r="D53">
+        <v>1</v>
+      </c>
+      <c r="E53">
+        <v>1.2</v>
+      </c>
+      <c r="F53">
+        <v>1.2</v>
+      </c>
+      <c r="G53">
+        <v>1.9</v>
+      </c>
+      <c r="H53">
+        <v>1.9</v>
+      </c>
+      <c r="I53">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>38</v>
+      </c>
+      <c r="B54">
+        <v>0</v>
+      </c>
+      <c r="C54">
+        <v>0</v>
+      </c>
+      <c r="D54">
+        <v>0</v>
+      </c>
+      <c r="E54">
+        <v>0</v>
+      </c>
+      <c r="F54">
+        <v>0</v>
+      </c>
+      <c r="G54">
+        <v>0</v>
+      </c>
+      <c r="H54">
+        <v>0</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>39</v>
+      </c>
+      <c r="B55">
+        <v>0</v>
+      </c>
+      <c r="C55">
+        <v>0</v>
+      </c>
+      <c r="D55">
+        <v>0</v>
+      </c>
+      <c r="E55">
+        <v>0</v>
+      </c>
+      <c r="F55">
+        <v>0</v>
+      </c>
+      <c r="G55">
+        <v>0</v>
+      </c>
+      <c r="H55">
+        <v>0</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{304F709B-7702-4C43-965F-DD204CE2661C}">
   <dimension ref="A1:M28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -4690,7 +9349,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2FDD259F-D2CD-4F5D-AEBF-5E701B59CE06}">
   <dimension ref="A1:J39"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -5550,7 +10209,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6ECF5878-620A-4B6F-9F42-0EB57194C8D1}">
   <dimension ref="A1:F27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -5949,7 +10608,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC8D546C-26AF-4F1F-ABF1-B4BB56273817}">
   <dimension ref="A1:G32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -6222,7 +10881,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B29C4515-FED8-46B3-A2D1-F267BB3C4D08}">
   <dimension ref="A1:K47"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -7272,7 +11931,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB9A2F52-9080-490D-91F1-658B5B0AADC8}">
   <dimension ref="A1:L26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -7954,1221 +12613,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8EC04B4-F8B6-4270-845C-06CD900EF148}">
-  <dimension ref="A1:L28"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="13.85546875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" t="s">
-        <v>73</v>
-      </c>
-      <c r="C3" t="s">
-        <v>73</v>
-      </c>
-      <c r="D3" t="s">
-        <v>73</v>
-      </c>
-      <c r="E3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F3" t="s">
-        <v>129</v>
-      </c>
-      <c r="G3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K3" t="s">
-        <v>130</v>
-      </c>
-      <c r="L3" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" t="s">
-        <v>13</v>
-      </c>
-      <c r="G4" t="s">
-        <v>12</v>
-      </c>
-      <c r="H4" t="s">
-        <v>13</v>
-      </c>
-      <c r="I4" t="s">
-        <v>15</v>
-      </c>
-      <c r="J4" t="s">
-        <v>14</v>
-      </c>
-      <c r="K4" t="s">
-        <v>18</v>
-      </c>
-      <c r="L4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>138</v>
-      </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
-      <c r="E6">
-        <v>4</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
-      <c r="J6">
-        <v>1</v>
-      </c>
-      <c r="K6">
-        <v>1</v>
-      </c>
-      <c r="L6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>139</v>
-      </c>
-      <c r="B7">
-        <v>1</v>
-      </c>
-      <c r="C7">
-        <v>0</v>
-      </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
-      <c r="E7">
-        <v>4</v>
-      </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
-      <c r="G7">
-        <v>1</v>
-      </c>
-      <c r="H7">
-        <v>0</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7">
-        <v>0</v>
-      </c>
-      <c r="K7">
-        <v>2</v>
-      </c>
-      <c r="L7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>140</v>
-      </c>
-      <c r="B8">
-        <v>0</v>
-      </c>
-      <c r="C8">
-        <v>0</v>
-      </c>
-      <c r="D8">
-        <v>1</v>
-      </c>
-      <c r="E8">
-        <v>4</v>
-      </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
-      <c r="I8">
-        <v>0</v>
-      </c>
-      <c r="J8">
-        <v>1</v>
-      </c>
-      <c r="K8">
-        <v>0</v>
-      </c>
-      <c r="L8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>141</v>
-      </c>
-      <c r="B9">
-        <v>0</v>
-      </c>
-      <c r="C9">
-        <v>1</v>
-      </c>
-      <c r="D9">
-        <v>0</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-      <c r="F9">
-        <v>4</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="H9">
-        <v>0</v>
-      </c>
-      <c r="I9">
-        <v>0</v>
-      </c>
-      <c r="J9">
-        <v>1</v>
-      </c>
-      <c r="K9">
-        <v>1</v>
-      </c>
-      <c r="L9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>142</v>
-      </c>
-      <c r="B10">
-        <v>1</v>
-      </c>
-      <c r="C10">
-        <v>0</v>
-      </c>
-      <c r="D10">
-        <v>0</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-      <c r="F10">
-        <v>4</v>
-      </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
-      <c r="H10">
-        <v>1</v>
-      </c>
-      <c r="I10">
-        <v>0</v>
-      </c>
-      <c r="J10">
-        <v>0</v>
-      </c>
-      <c r="K10">
-        <v>2</v>
-      </c>
-      <c r="L10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>143</v>
-      </c>
-      <c r="B11">
-        <v>0</v>
-      </c>
-      <c r="C11">
-        <v>1</v>
-      </c>
-      <c r="D11">
-        <v>0</v>
-      </c>
-      <c r="E11">
-        <v>4</v>
-      </c>
-      <c r="F11">
-        <v>0</v>
-      </c>
-      <c r="G11">
-        <v>1</v>
-      </c>
-      <c r="H11">
-        <v>0</v>
-      </c>
-      <c r="I11">
-        <v>0</v>
-      </c>
-      <c r="J11">
-        <v>0</v>
-      </c>
-      <c r="K11">
-        <v>2</v>
-      </c>
-      <c r="L11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>144</v>
-      </c>
-      <c r="B12">
-        <v>1</v>
-      </c>
-      <c r="C12">
-        <v>0</v>
-      </c>
-      <c r="D12">
-        <v>0</v>
-      </c>
-      <c r="E12">
-        <v>4</v>
-      </c>
-      <c r="F12">
-        <v>0</v>
-      </c>
-      <c r="G12">
-        <v>0</v>
-      </c>
-      <c r="H12">
-        <v>0</v>
-      </c>
-      <c r="I12">
-        <v>1</v>
-      </c>
-      <c r="J12">
-        <v>0</v>
-      </c>
-      <c r="K12">
-        <v>1</v>
-      </c>
-      <c r="L12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>21</v>
-      </c>
-      <c r="B14">
-        <v>1</v>
-      </c>
-      <c r="C14">
-        <v>1</v>
-      </c>
-      <c r="D14">
-        <v>1</v>
-      </c>
-      <c r="E14">
-        <v>4</v>
-      </c>
-      <c r="F14">
-        <v>4</v>
-      </c>
-      <c r="G14">
-        <v>1</v>
-      </c>
-      <c r="H14">
-        <v>1</v>
-      </c>
-      <c r="I14">
-        <v>1</v>
-      </c>
-      <c r="J14">
-        <v>1</v>
-      </c>
-      <c r="K14">
-        <v>2</v>
-      </c>
-      <c r="L14">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>22</v>
-      </c>
-      <c r="B16">
-        <v>0</v>
-      </c>
-      <c r="C16">
-        <v>0</v>
-      </c>
-      <c r="D16">
-        <v>0</v>
-      </c>
-      <c r="E16">
-        <v>0</v>
-      </c>
-      <c r="F16">
-        <v>0</v>
-      </c>
-      <c r="G16">
-        <v>0</v>
-      </c>
-      <c r="H16">
-        <v>0</v>
-      </c>
-      <c r="I16">
-        <v>0</v>
-      </c>
-      <c r="J16">
-        <v>0</v>
-      </c>
-      <c r="K16">
-        <v>0</v>
-      </c>
-      <c r="L16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>23</v>
-      </c>
-      <c r="B17">
-        <v>1</v>
-      </c>
-      <c r="C17">
-        <v>1</v>
-      </c>
-      <c r="D17">
-        <v>1</v>
-      </c>
-      <c r="E17">
-        <v>1</v>
-      </c>
-      <c r="F17">
-        <v>1</v>
-      </c>
-      <c r="G17">
-        <v>1</v>
-      </c>
-      <c r="H17">
-        <v>1</v>
-      </c>
-      <c r="I17">
-        <v>1</v>
-      </c>
-      <c r="J17">
-        <v>1</v>
-      </c>
-      <c r="K17">
-        <v>1</v>
-      </c>
-      <c r="L17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>24</v>
-      </c>
-      <c r="B18">
-        <f>1/15</f>
-        <v>6.6666666666666666E-2</v>
-      </c>
-      <c r="C18">
-        <f t="shared" ref="C18:L18" si="0">1/15</f>
-        <v>6.6666666666666666E-2</v>
-      </c>
-      <c r="D18">
-        <f t="shared" si="0"/>
-        <v>6.6666666666666666E-2</v>
-      </c>
-      <c r="E18">
-        <f t="shared" si="0"/>
-        <v>6.6666666666666666E-2</v>
-      </c>
-      <c r="F18">
-        <f t="shared" si="0"/>
-        <v>6.6666666666666666E-2</v>
-      </c>
-      <c r="G18">
-        <f t="shared" si="0"/>
-        <v>6.6666666666666666E-2</v>
-      </c>
-      <c r="H18">
-        <f t="shared" si="0"/>
-        <v>6.6666666666666666E-2</v>
-      </c>
-      <c r="I18">
-        <f t="shared" si="0"/>
-        <v>6.6666666666666666E-2</v>
-      </c>
-      <c r="J18">
-        <f t="shared" si="0"/>
-        <v>6.6666666666666666E-2</v>
-      </c>
-      <c r="K18">
-        <f t="shared" si="0"/>
-        <v>6.6666666666666666E-2</v>
-      </c>
-      <c r="L18">
-        <f t="shared" si="0"/>
-        <v>6.6666666666666666E-2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>25</v>
-      </c>
-      <c r="B19">
-        <v>0</v>
-      </c>
-      <c r="C19">
-        <v>0</v>
-      </c>
-      <c r="D19">
-        <v>0</v>
-      </c>
-      <c r="E19">
-        <v>0</v>
-      </c>
-      <c r="F19">
-        <v>0</v>
-      </c>
-      <c r="G19">
-        <v>0</v>
-      </c>
-      <c r="H19">
-        <v>0</v>
-      </c>
-      <c r="I19">
-        <v>0</v>
-      </c>
-      <c r="J19">
-        <v>0</v>
-      </c>
-      <c r="K19">
-        <v>0</v>
-      </c>
-      <c r="L19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>26</v>
-      </c>
-      <c r="B21" t="s">
-        <v>131</v>
-      </c>
-      <c r="C21" t="s">
-        <v>132</v>
-      </c>
-      <c r="D21" t="s">
-        <v>133</v>
-      </c>
-      <c r="E21" t="s">
-        <v>134</v>
-      </c>
-      <c r="F21" t="s">
-        <v>135</v>
-      </c>
-      <c r="G21" t="s">
-        <v>136</v>
-      </c>
-      <c r="H21" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>131</v>
-      </c>
-      <c r="B22">
-        <v>0</v>
-      </c>
-      <c r="C22">
-        <v>17000</v>
-      </c>
-      <c r="D22">
-        <v>17000</v>
-      </c>
-      <c r="E22">
-        <v>20000</v>
-      </c>
-      <c r="F22">
-        <v>30000</v>
-      </c>
-      <c r="G22">
-        <v>21000</v>
-      </c>
-      <c r="H22">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>132</v>
-      </c>
-      <c r="B23">
-        <v>17000</v>
-      </c>
-      <c r="C23">
-        <v>0</v>
-      </c>
-      <c r="D23">
-        <v>16000</v>
-      </c>
-      <c r="E23">
-        <v>37000</v>
-      </c>
-      <c r="F23">
-        <v>20000</v>
-      </c>
-      <c r="G23">
-        <v>4000</v>
-      </c>
-      <c r="H23">
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>133</v>
-      </c>
-      <c r="B24">
-        <v>17000</v>
-      </c>
-      <c r="C24">
-        <v>16000</v>
-      </c>
-      <c r="D24">
-        <v>0</v>
-      </c>
-      <c r="E24">
-        <v>30000</v>
-      </c>
-      <c r="F24">
-        <v>29000</v>
-      </c>
-      <c r="G24">
-        <v>13000</v>
-      </c>
-      <c r="H24">
-        <v>19000</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>134</v>
-      </c>
-      <c r="B25">
-        <v>20000</v>
-      </c>
-      <c r="C25">
-        <v>37000</v>
-      </c>
-      <c r="D25">
-        <v>30000</v>
-      </c>
-      <c r="E25">
-        <v>0</v>
-      </c>
-      <c r="F25">
-        <v>18000</v>
-      </c>
-      <c r="G25">
-        <v>33000</v>
-      </c>
-      <c r="H25">
-        <v>22000</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>135</v>
-      </c>
-      <c r="B26">
-        <v>30000</v>
-      </c>
-      <c r="C26">
-        <v>20000</v>
-      </c>
-      <c r="D26">
-        <v>29000</v>
-      </c>
-      <c r="E26">
-        <v>18000</v>
-      </c>
-      <c r="F26">
-        <v>0</v>
-      </c>
-      <c r="G26">
-        <v>24000</v>
-      </c>
-      <c r="H26">
-        <v>28600</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>136</v>
-      </c>
-      <c r="B27">
-        <v>21000</v>
-      </c>
-      <c r="C27">
-        <v>4000</v>
-      </c>
-      <c r="D27">
-        <v>13000</v>
-      </c>
-      <c r="E27">
-        <v>33000</v>
-      </c>
-      <c r="F27">
-        <v>24000</v>
-      </c>
-      <c r="G27">
-        <v>0</v>
-      </c>
-      <c r="H27">
-        <v>19000</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>137</v>
-      </c>
-      <c r="B28">
-        <v>2000</v>
-      </c>
-      <c r="C28">
-        <v>15000</v>
-      </c>
-      <c r="D28">
-        <v>19000</v>
-      </c>
-      <c r="E28">
-        <v>22000</v>
-      </c>
-      <c r="F28">
-        <v>28600</v>
-      </c>
-      <c r="G28">
-        <v>19000</v>
-      </c>
-      <c r="H28">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75EE02EB-ADA8-400E-A64B-539138E19798}">
-  <dimension ref="A1:F35"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="11.140625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E3" t="s">
-        <v>128</v>
-      </c>
-      <c r="F3" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" t="s">
-        <v>14</v>
-      </c>
-      <c r="F4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>127</v>
-      </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
-      <c r="E6">
-        <v>1</v>
-      </c>
-      <c r="F6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>109</v>
-      </c>
-      <c r="B7">
-        <v>0</v>
-      </c>
-      <c r="C7">
-        <v>1</v>
-      </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
-      <c r="E7">
-        <v>2</v>
-      </c>
-      <c r="F7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>110</v>
-      </c>
-      <c r="B8">
-        <v>0</v>
-      </c>
-      <c r="C8">
-        <v>0</v>
-      </c>
-      <c r="D8">
-        <v>1</v>
-      </c>
-      <c r="E8">
-        <v>1</v>
-      </c>
-      <c r="F8">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>21</v>
-      </c>
-      <c r="B10">
-        <v>1</v>
-      </c>
-      <c r="C10">
-        <v>1</v>
-      </c>
-      <c r="D10">
-        <v>1</v>
-      </c>
-      <c r="E10">
-        <v>1</v>
-      </c>
-      <c r="F10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>22</v>
-      </c>
-      <c r="B12">
-        <v>0</v>
-      </c>
-      <c r="C12">
-        <v>0</v>
-      </c>
-      <c r="D12">
-        <v>0</v>
-      </c>
-      <c r="E12">
-        <v>0</v>
-      </c>
-      <c r="F12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>23</v>
-      </c>
-      <c r="B13">
-        <v>1</v>
-      </c>
-      <c r="C13">
-        <v>1</v>
-      </c>
-      <c r="D13">
-        <v>1</v>
-      </c>
-      <c r="E13">
-        <v>1</v>
-      </c>
-      <c r="F13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>24</v>
-      </c>
-      <c r="B14">
-        <v>6.7000000000000004E-2</v>
-      </c>
-      <c r="C14">
-        <v>6.7000000000000004E-2</v>
-      </c>
-      <c r="D14">
-        <v>6.7000000000000004E-2</v>
-      </c>
-      <c r="E14">
-        <v>6.7000000000000004E-2</v>
-      </c>
-      <c r="F14">
-        <v>6.7000000000000004E-2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>25</v>
-      </c>
-      <c r="B15">
-        <v>0</v>
-      </c>
-      <c r="C15">
-        <v>0</v>
-      </c>
-      <c r="D15">
-        <v>0</v>
-      </c>
-      <c r="E15">
-        <v>0</v>
-      </c>
-      <c r="F15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>26</v>
-      </c>
-      <c r="B17" t="s">
-        <v>111</v>
-      </c>
-      <c r="C17" t="s">
-        <v>106</v>
-      </c>
-      <c r="D17" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>111</v>
-      </c>
-      <c r="B18">
-        <v>0</v>
-      </c>
-      <c r="C18" s="5">
-        <v>14600</v>
-      </c>
-      <c r="D18" s="5">
-        <v>24100</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>106</v>
-      </c>
-      <c r="B19" s="5">
-        <v>14600</v>
-      </c>
-      <c r="C19">
-        <v>0</v>
-      </c>
-      <c r="D19" s="5">
-        <v>48500</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>107</v>
-      </c>
-      <c r="B20" s="5">
-        <v>24100</v>
-      </c>
-      <c r="C20" s="5">
-        <v>48500</v>
-      </c>
-      <c r="D20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>34</v>
-      </c>
-      <c r="B22" t="s">
-        <v>111</v>
-      </c>
-      <c r="C22" t="s">
-        <v>106</v>
-      </c>
-      <c r="D22" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>111</v>
-      </c>
-      <c r="B23">
-        <v>0</v>
-      </c>
-      <c r="C23">
-        <v>-9.35</v>
-      </c>
-      <c r="D23">
-        <v>-9.57</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>106</v>
-      </c>
-      <c r="B24">
-        <v>-9.35</v>
-      </c>
-      <c r="C24">
-        <v>0</v>
-      </c>
-      <c r="D24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>107</v>
-      </c>
-      <c r="B25">
-        <v>-9.57</v>
-      </c>
-      <c r="C25">
-        <v>0</v>
-      </c>
-      <c r="D25">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>35</v>
-      </c>
-      <c r="B27" t="s">
-        <v>111</v>
-      </c>
-      <c r="C27" t="s">
-        <v>106</v>
-      </c>
-      <c r="D27" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>111</v>
-      </c>
-      <c r="B28">
-        <v>0</v>
-      </c>
-      <c r="C28">
-        <v>-40</v>
-      </c>
-      <c r="D28" s="5">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>106</v>
-      </c>
-      <c r="B29">
-        <v>-40</v>
-      </c>
-      <c r="C29">
-        <v>0</v>
-      </c>
-      <c r="D29">
-        <v>-130</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>107</v>
-      </c>
-      <c r="B30" s="5">
-        <v>338</v>
-      </c>
-      <c r="C30">
-        <v>-130</v>
-      </c>
-      <c r="D30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>36</v>
-      </c>
-      <c r="B32" t="s">
-        <v>111</v>
-      </c>
-      <c r="C32" t="s">
-        <v>106</v>
-      </c>
-      <c r="D32" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>37</v>
-      </c>
-      <c r="B33">
-        <v>0.67400000000000004</v>
-      </c>
-      <c r="C33">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="D33">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>38</v>
-      </c>
-      <c r="B34">
-        <v>0</v>
-      </c>
-      <c r="C34">
-        <v>0</v>
-      </c>
-      <c r="D34">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>39</v>
-      </c>
-      <c r="B35">
-        <v>0</v>
-      </c>
-      <c r="C35">
-        <v>0</v>
-      </c>
-      <c r="D35">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/Solutions/Metabasite.xlsx
+++ b/Solutions/Metabasite.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dropbox\Thermolab\v_25_10_01\Solutions\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hans\Documents\GitHub\Thermolab\Solutions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{973424CC-BF31-4422-BCC0-51F0757452B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A47C9881-A06C-40B9-8B58-793F0A453D72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="46680" yWindow="2355" windowWidth="28800" windowHeight="15435" activeTab="3" xr2:uid="{A49E5DA2-E197-42C8-A9DC-E0DBAA94DA8C}"/>
+    <workbookView xWindow="19420" yWindow="3730" windowWidth="12630" windowHeight="16660" firstSheet="9" activeTab="14" xr2:uid="{A49E5DA2-E197-42C8-A9DC-E0DBAA94DA8C}"/>
   </bookViews>
   <sheets>
     <sheet name="Amphibole" sheetId="1" r:id="rId1"/>
@@ -42,9 +42,6 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -756,9 +753,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -796,7 +793,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -902,7 +899,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1044,7 +1041,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1053,9 +1050,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D89C5715-8989-484A-A444-9B08949E6D16}">
   <dimension ref="A1:S41"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1063,7 +1060,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -1122,7 +1119,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -1181,7 +1178,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>40</v>
       </c>
@@ -1240,7 +1237,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>41</v>
       </c>
@@ -1299,7 +1296,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>42</v>
       </c>
@@ -1358,7 +1355,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>43</v>
       </c>
@@ -1417,7 +1414,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>44</v>
       </c>
@@ -1476,7 +1473,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>45</v>
       </c>
@@ -1535,7 +1532,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>46</v>
       </c>
@@ -1594,7 +1591,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>47</v>
       </c>
@@ -1653,7 +1650,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>48</v>
       </c>
@@ -1712,7 +1709,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>49</v>
       </c>
@@ -1771,7 +1768,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>50</v>
       </c>
@@ -1830,7 +1827,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>21</v>
       </c>
@@ -1889,7 +1886,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>22</v>
       </c>
@@ -1948,7 +1945,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>23</v>
       </c>
@@ -2007,7 +2004,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>24</v>
       </c>
@@ -2084,7 +2081,7 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>25</v>
       </c>
@@ -2143,7 +2140,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>26</v>
       </c>
@@ -2181,7 +2178,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>27</v>
       </c>
@@ -2219,7 +2216,7 @@
         <v>85000</v>
       </c>
     </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>51</v>
       </c>
@@ -2257,7 +2254,7 @@
         <v>35000</v>
       </c>
     </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>52</v>
       </c>
@@ -2295,7 +2292,7 @@
         <v>15000</v>
       </c>
     </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>53</v>
       </c>
@@ -2333,7 +2330,7 @@
         <v>75000</v>
       </c>
     </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>28</v>
       </c>
@@ -2371,7 +2368,7 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>54</v>
       </c>
@@ -2409,7 +2406,7 @@
         <v>65000</v>
       </c>
     </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>29</v>
       </c>
@@ -2447,7 +2444,7 @@
         <v>95000</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>30</v>
       </c>
@@ -2485,7 +2482,7 @@
         <v>95000</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>31</v>
       </c>
@@ -2523,7 +2520,7 @@
         <v>50000</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>32</v>
       </c>
@@ -2561,7 +2558,7 @@
         <v>35000</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>33</v>
       </c>
@@ -2599,7 +2596,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>36</v>
       </c>
@@ -2637,7 +2634,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>37</v>
       </c>
@@ -2675,7 +2672,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>38</v>
       </c>
@@ -2713,7 +2710,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>39</v>
       </c>
@@ -2759,12 +2756,12 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8EC04B4-F8B6-4270-845C-06CD900EF148}">
   <dimension ref="A1:L28"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2772,7 +2769,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -2810,7 +2807,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -2848,7 +2845,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>138</v>
       </c>
@@ -2886,7 +2883,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>139</v>
       </c>
@@ -2924,7 +2921,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>140</v>
       </c>
@@ -2962,7 +2959,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>141</v>
       </c>
@@ -3000,7 +2997,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>142</v>
       </c>
@@ -3038,7 +3035,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>143</v>
       </c>
@@ -3076,7 +3073,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>144</v>
       </c>
@@ -3114,7 +3111,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>21</v>
       </c>
@@ -3152,7 +3149,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>22</v>
       </c>
@@ -3190,7 +3187,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>23</v>
       </c>
@@ -3228,7 +3225,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>24</v>
       </c>
@@ -3277,7 +3274,7 @@
         <v>6.6666666666666666E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>25</v>
       </c>
@@ -3315,7 +3312,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>26</v>
       </c>
@@ -3341,7 +3338,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>131</v>
       </c>
@@ -3367,7 +3364,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>132</v>
       </c>
@@ -3393,7 +3390,7 @@
         <v>15000</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>133</v>
       </c>
@@ -3419,7 +3416,7 @@
         <v>19000</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>134</v>
       </c>
@@ -3445,7 +3442,7 @@
         <v>22000</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>135</v>
       </c>
@@ -3471,7 +3468,7 @@
         <v>28600</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>136</v>
       </c>
@@ -3497,7 +3494,7 @@
         <v>19000</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>137</v>
       </c>
@@ -3531,12 +3528,12 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75EE02EB-ADA8-400E-A64B-539138E19798}">
   <dimension ref="A1:F35"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3544,7 +3541,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -3564,7 +3561,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -3584,7 +3581,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>127</v>
       </c>
@@ -3604,7 +3601,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>109</v>
       </c>
@@ -3624,7 +3621,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>110</v>
       </c>
@@ -3644,7 +3641,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>21</v>
       </c>
@@ -3664,7 +3661,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>22</v>
       </c>
@@ -3684,7 +3681,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>23</v>
       </c>
@@ -3704,7 +3701,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>24</v>
       </c>
@@ -3724,7 +3721,7 @@
         <v>6.7000000000000004E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>25</v>
       </c>
@@ -3744,7 +3741,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>26</v>
       </c>
@@ -3758,7 +3755,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>111</v>
       </c>
@@ -3772,7 +3769,7 @@
         <v>24100</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>106</v>
       </c>
@@ -3786,7 +3783,7 @@
         <v>48500</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>107</v>
       </c>
@@ -3800,7 +3797,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>34</v>
       </c>
@@ -3814,7 +3811,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>111</v>
       </c>
@@ -3828,7 +3825,7 @@
         <v>-9.57</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>106</v>
       </c>
@@ -3842,7 +3839,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>107</v>
       </c>
@@ -3856,7 +3853,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>35</v>
       </c>
@@ -3870,7 +3867,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>111</v>
       </c>
@@ -3884,7 +3881,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>106</v>
       </c>
@@ -3898,7 +3895,7 @@
         <v>-130</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>107</v>
       </c>
@@ -3912,7 +3909,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>36</v>
       </c>
@@ -3926,7 +3923,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>37</v>
       </c>
@@ -3940,7 +3937,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>38</v>
       </c>
@@ -3954,7 +3951,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>39</v>
       </c>
@@ -3976,9 +3973,9 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11D063D2-B63C-4FD4-B9C7-610F4E699550}">
   <dimension ref="A1:J35"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3986,7 +3983,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -4000,7 +3997,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -4014,7 +4011,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>108</v>
       </c>
@@ -4028,7 +4025,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>109</v>
       </c>
@@ -4042,7 +4039,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>110</v>
       </c>
@@ -4056,7 +4053,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>21</v>
       </c>
@@ -4070,7 +4067,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>22</v>
       </c>
@@ -4084,7 +4081,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>23</v>
       </c>
@@ -4098,7 +4095,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>24</v>
       </c>
@@ -4112,7 +4109,7 @@
         <v>6.7000000000000004E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>25</v>
       </c>
@@ -4126,7 +4123,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>26</v>
       </c>
@@ -4140,7 +4137,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>105</v>
       </c>
@@ -4156,7 +4153,7 @@
       <c r="I18" s="5"/>
       <c r="J18" s="5"/>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>106</v>
       </c>
@@ -4172,7 +4169,7 @@
       <c r="H19" s="5"/>
       <c r="J19" s="5"/>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>107</v>
       </c>
@@ -4188,7 +4185,7 @@
       <c r="H20" s="5"/>
       <c r="I20" s="5"/>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>34</v>
       </c>
@@ -4202,7 +4199,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>105</v>
       </c>
@@ -4216,7 +4213,7 @@
         <v>-10.8</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>106</v>
       </c>
@@ -4230,7 +4227,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>107</v>
       </c>
@@ -4244,7 +4241,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>35</v>
       </c>
@@ -4258,7 +4255,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>105</v>
       </c>
@@ -4273,7 +4270,7 @@
       </c>
       <c r="J28" s="5"/>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>106</v>
       </c>
@@ -4287,7 +4284,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>107</v>
       </c>
@@ -4302,7 +4299,7 @@
       </c>
       <c r="H30" s="5"/>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>36</v>
       </c>
@@ -4316,7 +4313,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>37</v>
       </c>
@@ -4330,7 +4327,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>38</v>
       </c>
@@ -4344,7 +4341,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>39</v>
       </c>
@@ -4366,12 +4363,12 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{562841B5-2CE3-4AF4-B924-12DA9A538BCD}">
   <dimension ref="A1:G24"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4379,7 +4376,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -4402,7 +4399,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -4425,7 +4422,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>161</v>
       </c>
@@ -4448,7 +4445,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>162</v>
       </c>
@@ -4471,7 +4468,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>163</v>
       </c>
@@ -4494,7 +4491,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>21</v>
       </c>
@@ -4517,7 +4514,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>22</v>
       </c>
@@ -4540,7 +4537,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>23</v>
       </c>
@@ -4563,7 +4560,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>24</v>
       </c>
@@ -4586,7 +4583,7 @@
         <v>6.7000000000000004E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>25</v>
       </c>
@@ -4609,7 +4606,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>26</v>
       </c>
@@ -4623,7 +4620,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>158</v>
       </c>
@@ -4637,7 +4634,7 @@
         <v>26600</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>159</v>
       </c>
@@ -4651,7 +4648,7 @@
         <v>11000</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>160</v>
       </c>
@@ -4665,10 +4662,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="D22" s="5"/>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B24" s="5"/>
     </row>
   </sheetData>
@@ -4679,12 +4676,12 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A2380B6-156D-48B4-B01F-F11751B6C129}">
   <dimension ref="A1:E23"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4692,7 +4689,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -4703,7 +4700,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -4714,7 +4711,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>166</v>
       </c>
@@ -4727,7 +4724,7 @@
       <c r="D6" s="6"/>
       <c r="E6" s="6"/>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>167</v>
       </c>
@@ -4740,7 +4737,7 @@
       <c r="D7" s="6"/>
       <c r="E7" s="6"/>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>21</v>
       </c>
@@ -4751,7 +4748,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>22</v>
       </c>
@@ -4762,7 +4759,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>23</v>
       </c>
@@ -4773,7 +4770,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>24</v>
       </c>
@@ -4786,7 +4783,7 @@
         <v>6.6666666666666666E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>25</v>
       </c>
@@ -4797,7 +4794,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>26</v>
       </c>
@@ -4808,7 +4805,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>164</v>
       </c>
@@ -4820,7 +4817,7 @@
       </c>
       <c r="D17" s="5"/>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>165</v>
       </c>
@@ -4832,7 +4829,7 @@
       </c>
       <c r="D18" s="5"/>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>36</v>
       </c>
@@ -4843,7 +4840,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>37</v>
       </c>
@@ -4854,7 +4851,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>38</v>
       </c>
@@ -4865,7 +4862,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>39</v>
       </c>
@@ -4884,9 +4881,9 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7CA70AFB-945D-490B-B834-AC2D41D28234}">
   <dimension ref="A1:F22"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4894,7 +4891,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -4914,7 +4911,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -4934,7 +4931,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>171</v>
       </c>
@@ -4954,7 +4951,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>172</v>
       </c>
@@ -4974,7 +4971,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>173</v>
       </c>
@@ -4994,7 +4991,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>174</v>
       </c>
@@ -5014,7 +5011,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>21</v>
       </c>
@@ -5034,7 +5031,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>22</v>
       </c>
@@ -5054,7 +5051,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>23</v>
       </c>
@@ -5074,7 +5071,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>24</v>
       </c>
@@ -5094,7 +5091,7 @@
         <v>6.7000000000000004E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>25</v>
       </c>
@@ -5114,7 +5111,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>26</v>
       </c>
@@ -5131,7 +5128,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>168</v>
       </c>
@@ -5148,7 +5145,7 @@
         <v>27000</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>169</v>
       </c>
@@ -5165,7 +5162,7 @@
         <v>30000</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>170</v>
       </c>
@@ -5182,7 +5179,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>175</v>
       </c>
@@ -5207,15 +5204,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{235766CB-85E5-4E00-A98A-A35D6EFE0C78}">
   <dimension ref="A1:O59"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="14.42578125" customWidth="1"/>
+    <col min="1" max="1" width="14.453125" customWidth="1"/>
     <col min="2" max="4" width="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.140625" customWidth="1"/>
+    <col min="5" max="5" width="9.1796875" customWidth="1"/>
     <col min="7" max="8" width="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -5223,7 +5220,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -5263,7 +5260,7 @@
       <c r="N3" s="7"/>
       <c r="O3" s="7"/>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -5301,7 +5298,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>177</v>
       </c>
@@ -5341,7 +5338,7 @@
       <c r="N6" s="6"/>
       <c r="O6" s="6"/>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>178</v>
       </c>
@@ -5381,7 +5378,7 @@
       <c r="N7" s="6"/>
       <c r="O7" s="6"/>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>179</v>
       </c>
@@ -5421,7 +5418,7 @@
       <c r="N8" s="6"/>
       <c r="O8" s="6"/>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>188</v>
       </c>
@@ -5461,7 +5458,7 @@
       <c r="N9" s="6"/>
       <c r="O9" s="6"/>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>189</v>
       </c>
@@ -5501,7 +5498,7 @@
       <c r="N10" s="6"/>
       <c r="O10" s="6"/>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>197</v>
       </c>
@@ -5541,7 +5538,7 @@
       <c r="N11" s="6"/>
       <c r="O11" s="6"/>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>196</v>
       </c>
@@ -5581,7 +5578,7 @@
       <c r="N12" s="6"/>
       <c r="O12" s="6"/>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>180</v>
       </c>
@@ -5621,7 +5618,7 @@
       <c r="N13" s="6"/>
       <c r="O13" s="6"/>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>190</v>
       </c>
@@ -5661,7 +5658,7 @@
       <c r="N14" s="6"/>
       <c r="O14" s="6"/>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>21</v>
       </c>
@@ -5701,7 +5698,7 @@
       <c r="N16" s="6"/>
       <c r="O16" s="6"/>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>22</v>
       </c>
@@ -5741,7 +5738,7 @@
       <c r="N18" s="6"/>
       <c r="O18" s="6"/>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>23</v>
       </c>
@@ -5781,7 +5778,7 @@
       <c r="N19" s="6"/>
       <c r="O19" s="6"/>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>24</v>
       </c>
@@ -5832,7 +5829,7 @@
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>25</v>
       </c>
@@ -5870,11 +5867,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.35">
       <c r="J22" s="6"/>
       <c r="K22" s="6"/>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>26</v>
       </c>
@@ -5906,7 +5903,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>181</v>
       </c>
@@ -5938,7 +5935,7 @@
         <v>-29500</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>182</v>
       </c>
@@ -5970,7 +5967,7 @@
         <v>8600</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>183</v>
       </c>
@@ -6002,7 +5999,7 @@
         <v>-16000</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>192</v>
       </c>
@@ -6034,7 +6031,7 @@
         <v>3500</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>184</v>
       </c>
@@ -6066,7 +6063,7 @@
         <v>6400</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>186</v>
       </c>
@@ -6098,7 +6095,7 @@
         <v>-43500</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>185</v>
       </c>
@@ -6130,7 +6127,7 @@
         <v>-26000</v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>187</v>
       </c>
@@ -6162,7 +6159,7 @@
         <v>9750</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>195</v>
       </c>
@@ -6194,7 +6191,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>34</v>
       </c>
@@ -6226,7 +6223,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>181</v>
       </c>
@@ -6258,7 +6255,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>182</v>
       </c>
@@ -6290,7 +6287,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>183</v>
       </c>
@@ -6322,7 +6319,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>192</v>
       </c>
@@ -6354,7 +6351,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>184</v>
       </c>
@@ -6386,7 +6383,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>186</v>
       </c>
@@ -6418,7 +6415,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>185</v>
       </c>
@@ -6450,7 +6447,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>187</v>
       </c>
@@ -6482,7 +6479,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>195</v>
       </c>
@@ -6514,7 +6511,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B44" s="6"/>
       <c r="C44" s="6"/>
       <c r="D44" s="6"/>
@@ -6524,7 +6521,7 @@
       <c r="H44" s="6"/>
       <c r="I44" s="6"/>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>35</v>
       </c>
@@ -6556,7 +6553,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>181</v>
       </c>
@@ -6588,7 +6585,7 @@
         <v>-100</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>182</v>
       </c>
@@ -6620,7 +6617,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>183</v>
       </c>
@@ -6652,7 +6649,7 @@
         <v>-250</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>192</v>
       </c>
@@ -6684,7 +6681,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>184</v>
       </c>
@@ -6716,7 +6713,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>186</v>
       </c>
@@ -6748,7 +6745,7 @@
         <v>-950</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>185</v>
       </c>
@@ -6780,7 +6777,7 @@
         <v>-600</v>
       </c>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>187</v>
       </c>
@@ -6812,7 +6809,7 @@
         <v>-500</v>
       </c>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>195</v>
       </c>
@@ -6844,13 +6841,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B55" s="6"/>
       <c r="C55" s="6"/>
       <c r="D55" s="6"/>
       <c r="E55" s="6"/>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>36</v>
       </c>
@@ -6882,7 +6879,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>37</v>
       </c>
@@ -6914,7 +6911,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>38</v>
       </c>
@@ -6946,7 +6943,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>39</v>
       </c>
@@ -6986,12 +6983,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{956F8C11-B9B7-488A-A996-46E9938D33E3}">
   <dimension ref="A1:M55"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6999,7 +6996,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -7040,7 +7037,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -7081,7 +7078,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>66</v>
       </c>
@@ -7122,7 +7119,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>200</v>
       </c>
@@ -7163,7 +7160,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>201</v>
       </c>
@@ -7204,7 +7201,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>202</v>
       </c>
@@ -7245,7 +7242,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>212</v>
       </c>
@@ -7286,7 +7283,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>203</v>
       </c>
@@ -7327,7 +7324,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>204</v>
       </c>
@@ -7368,7 +7365,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>205</v>
       </c>
@@ -7409,7 +7406,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
@@ -7423,7 +7420,7 @@
       <c r="L14" s="1"/>
       <c r="M14" s="1"/>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>21</v>
       </c>
@@ -7464,7 +7461,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>22</v>
       </c>
@@ -7505,7 +7502,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>23</v>
       </c>
@@ -7546,7 +7543,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>24</v>
       </c>
@@ -7587,7 +7584,7 @@
         <v>6.7000000000000004E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>25</v>
       </c>
@@ -7628,7 +7625,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>26</v>
       </c>
@@ -7657,7 +7654,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>66</v>
       </c>
@@ -7686,7 +7683,7 @@
         <v>20600</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>200</v>
       </c>
@@ -7715,7 +7712,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>201</v>
       </c>
@@ -7744,7 +7741,7 @@
         <v>3500</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>202</v>
       </c>
@@ -7773,7 +7770,7 @@
         <v>40000</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>68</v>
       </c>
@@ -7802,7 +7799,7 @@
         <v>60000</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>203</v>
       </c>
@@ -7831,7 +7828,7 @@
         <v>50000</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>204</v>
       </c>
@@ -7860,7 +7857,7 @@
         <v>50000</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>205</v>
       </c>
@@ -7889,7 +7886,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>34</v>
       </c>
@@ -7918,7 +7915,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>66</v>
       </c>
@@ -7947,7 +7944,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>200</v>
       </c>
@@ -7976,7 +7973,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>201</v>
       </c>
@@ -8005,7 +8002,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>202</v>
       </c>
@@ -8034,7 +8031,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>68</v>
       </c>
@@ -8063,7 +8060,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>203</v>
       </c>
@@ -8092,7 +8089,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>204</v>
       </c>
@@ -8121,7 +8118,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>205</v>
       </c>
@@ -8150,7 +8147,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>35</v>
       </c>
@@ -8179,7 +8176,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>66</v>
       </c>
@@ -8208,7 +8205,7 @@
         <v>-30</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>200</v>
       </c>
@@ -8237,7 +8234,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>201</v>
       </c>
@@ -8266,7 +8263,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>202</v>
       </c>
@@ -8295,7 +8292,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>68</v>
       </c>
@@ -8324,7 +8321,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>203</v>
       </c>
@@ -8353,7 +8350,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>204</v>
       </c>
@@ -8382,7 +8379,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>205</v>
       </c>
@@ -8411,7 +8408,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>36</v>
       </c>
@@ -8440,7 +8437,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>37</v>
       </c>
@@ -8469,7 +8466,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>38</v>
       </c>
@@ -8498,7 +8495,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>39</v>
       </c>
@@ -8535,12 +8532,12 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{304F709B-7702-4C43-965F-DD204CE2661C}">
   <dimension ref="A1:M28"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -8548,7 +8545,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -8589,7 +8586,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -8630,7 +8627,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>65</v>
       </c>
@@ -8671,7 +8668,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>66</v>
       </c>
@@ -8712,7 +8709,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>67</v>
       </c>
@@ -8753,7 +8750,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>68</v>
       </c>
@@ -8794,7 +8791,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>69</v>
       </c>
@@ -8835,7 +8832,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>70</v>
       </c>
@@ -8876,7 +8873,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>71</v>
       </c>
@@ -8917,7 +8914,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
@@ -8931,7 +8928,7 @@
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>21</v>
       </c>
@@ -8972,7 +8969,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>22</v>
       </c>
@@ -9013,7 +9010,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>23</v>
       </c>
@@ -9054,7 +9051,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>24</v>
       </c>
@@ -9095,7 +9092,7 @@
         <v>6.7000000000000004E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>25</v>
       </c>
@@ -9136,7 +9133,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>26</v>
       </c>
@@ -9162,7 +9159,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>59</v>
       </c>
@@ -9188,7 +9185,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>60</v>
       </c>
@@ -9214,7 +9211,7 @@
         <v>24650</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>61</v>
       </c>
@@ -9240,7 +9237,7 @@
         <v>24600</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>72</v>
       </c>
@@ -9266,7 +9263,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>62</v>
       </c>
@@ -9292,7 +9289,7 @@
         <v>19500</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>63</v>
       </c>
@@ -9318,7 +9315,7 @@
         <v>24550</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>64</v>
       </c>
@@ -9352,12 +9349,12 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2FDD259F-D2CD-4F5D-AEBF-5E701B59CE06}">
   <dimension ref="A1:J39"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9365,7 +9362,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -9397,7 +9394,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -9429,7 +9426,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>150</v>
       </c>
@@ -9461,7 +9458,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>151</v>
       </c>
@@ -9493,7 +9490,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>152</v>
       </c>
@@ -9525,7 +9522,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>153</v>
       </c>
@@ -9557,7 +9554,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>154</v>
       </c>
@@ -9589,7 +9586,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>155</v>
       </c>
@@ -9621,7 +9618,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>21</v>
       </c>
@@ -9653,7 +9650,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>22</v>
       </c>
@@ -9685,7 +9682,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>23</v>
       </c>
@@ -9717,7 +9714,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>24</v>
       </c>
@@ -9758,7 +9755,7 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>25</v>
       </c>
@@ -9790,7 +9787,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>26</v>
       </c>
@@ -9813,7 +9810,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>145</v>
       </c>
@@ -9836,7 +9833,7 @@
         <v>32200.000000000004</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>146</v>
       </c>
@@ -9859,7 +9856,7 @@
         <v>25540</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>147</v>
       </c>
@@ -9882,7 +9879,7 @@
         <v>22540</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>149</v>
       </c>
@@ -9905,7 +9902,7 @@
         <v>75400</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>156</v>
       </c>
@@ -9928,7 +9925,7 @@
         <v>73400</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>148</v>
       </c>
@@ -9951,7 +9948,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>35</v>
       </c>
@@ -9974,7 +9971,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>145</v>
       </c>
@@ -9997,7 +9994,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>146</v>
       </c>
@@ -10020,7 +10017,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>147</v>
       </c>
@@ -10043,7 +10040,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>149</v>
       </c>
@@ -10066,7 +10063,7 @@
         <v>-940</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>156</v>
       </c>
@@ -10089,7 +10086,7 @@
         <v>-940</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>148</v>
       </c>
@@ -10112,7 +10109,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>36</v>
       </c>
@@ -10135,7 +10132,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>37</v>
       </c>
@@ -10158,7 +10155,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>38</v>
       </c>
@@ -10181,7 +10178,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>39</v>
       </c>
@@ -10212,12 +10209,12 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6ECF5878-620A-4B6F-9F42-0EB57194C8D1}">
   <dimension ref="A1:F27"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -10225,7 +10222,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -10245,7 +10242,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -10265,7 +10262,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
         <v>78</v>
       </c>
@@ -10285,7 +10282,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>79</v>
       </c>
@@ -10305,7 +10302,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>80</v>
       </c>
@@ -10325,7 +10322,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>77</v>
       </c>
@@ -10345,7 +10342,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>21</v>
       </c>
@@ -10365,7 +10362,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>22</v>
       </c>
@@ -10385,7 +10382,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>23</v>
       </c>
@@ -10405,7 +10402,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>24</v>
       </c>
@@ -10430,7 +10427,7 @@
         <v>6.6666666666666666E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>25</v>
       </c>
@@ -10450,7 +10447,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>26</v>
       </c>
@@ -10467,7 +10464,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" s="4" t="s">
         <v>74</v>
       </c>
@@ -10484,7 +10481,7 @@
         <v>5400</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>75</v>
       </c>
@@ -10501,7 +10498,7 @@
         <v>22600</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>76</v>
       </c>
@@ -10518,7 +10515,7 @@
         <v>-15300</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>83</v>
       </c>
@@ -10535,7 +10532,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>36</v>
       </c>
@@ -10552,7 +10549,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>37</v>
       </c>
@@ -10569,7 +10566,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>38</v>
       </c>
@@ -10586,7 +10583,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>39</v>
       </c>
@@ -10611,9 +10608,9 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC8D546C-26AF-4F1F-ABF1-B4BB56273817}">
   <dimension ref="A1:G32"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -10621,7 +10618,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -10638,75 +10635,75 @@
         <v>84</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>8</v>
       </c>
       <c r="B4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" t="s">
         <v>14</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>15</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>14</v>
       </c>
-      <c r="E4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>102</v>
       </c>
       <c r="B6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>103</v>
       </c>
       <c r="B7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>104</v>
       </c>
       <c r="B8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>21</v>
       </c>
@@ -10723,7 +10720,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>22</v>
       </c>
@@ -10740,7 +10737,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>23</v>
       </c>
@@ -10756,9 +10753,8 @@
       <c r="E13">
         <v>1</v>
       </c>
-      <c r="F13" s="5"/>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>24</v>
       </c>
@@ -10774,9 +10770,8 @@
       <c r="E14">
         <v>6.7000000000000004E-2</v>
       </c>
-      <c r="F14" s="5"/>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>25</v>
       </c>
@@ -10792,13 +10787,12 @@
       <c r="E15">
         <v>0</v>
       </c>
-      <c r="F15" s="5"/>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="F16" s="5"/>
       <c r="G16" s="5"/>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>26</v>
       </c>
@@ -10814,7 +10808,7 @@
       <c r="E17" s="5"/>
       <c r="G17" s="5"/>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>85</v>
       </c>
@@ -10830,7 +10824,7 @@
       <c r="E18" s="5"/>
       <c r="F18" s="5"/>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>86</v>
       </c>
@@ -10844,7 +10838,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>87</v>
       </c>
@@ -10858,20 +10852,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
       <c r="C29" s="5"/>
       <c r="D29" s="5"/>
       <c r="E29" s="5"/>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B30" s="5"/>
       <c r="E30" s="5"/>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B31" s="5"/>
       <c r="E31" s="5"/>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B32" s="5"/>
       <c r="C32" s="5"/>
       <c r="D32" s="5"/>
@@ -10884,9 +10878,9 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B29C4515-FED8-46B3-A2D1-F267BB3C4D08}">
   <dimension ref="A1:K47"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -10894,7 +10888,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -10929,7 +10923,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -10964,7 +10958,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>96</v>
       </c>
@@ -10999,7 +10993,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>97</v>
       </c>
@@ -11034,7 +11028,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>98</v>
       </c>
@@ -11069,7 +11063,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>99</v>
       </c>
@@ -11104,7 +11098,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>100</v>
       </c>
@@ -11139,7 +11133,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>101</v>
       </c>
@@ -11174,7 +11168,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>21</v>
       </c>
@@ -11209,7 +11203,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>22</v>
       </c>
@@ -11244,7 +11238,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>23</v>
       </c>
@@ -11279,7 +11273,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>24</v>
       </c>
@@ -11314,7 +11308,7 @@
         <v>6.7000000000000004E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>25</v>
       </c>
@@ -11349,7 +11343,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>26</v>
       </c>
@@ -11372,7 +11366,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>90</v>
       </c>
@@ -11395,7 +11389,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>91</v>
       </c>
@@ -11418,7 +11412,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>92</v>
       </c>
@@ -11441,7 +11435,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>93</v>
       </c>
@@ -11464,7 +11458,7 @@
         <v>30000</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>94</v>
       </c>
@@ -11487,7 +11481,7 @@
         <v>35000</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>95</v>
       </c>
@@ -11510,7 +11504,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>34</v>
       </c>
@@ -11533,7 +11527,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>90</v>
       </c>
@@ -11557,7 +11551,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>91</v>
       </c>
@@ -11580,7 +11574,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>92</v>
       </c>
@@ -11603,7 +11597,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>93</v>
       </c>
@@ -11627,7 +11621,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>94</v>
       </c>
@@ -11650,7 +11644,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>95</v>
       </c>
@@ -11673,7 +11667,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>35</v>
       </c>
@@ -11696,7 +11690,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>90</v>
       </c>
@@ -11719,7 +11713,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>91</v>
       </c>
@@ -11742,7 +11736,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>92</v>
       </c>
@@ -11765,7 +11759,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>93</v>
       </c>
@@ -11788,7 +11782,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>94</v>
       </c>
@@ -11811,7 +11805,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>95</v>
       </c>
@@ -11834,7 +11828,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>36</v>
       </c>
@@ -11857,7 +11851,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>37</v>
       </c>
@@ -11880,7 +11874,7 @@
         <v>0.63</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>38</v>
       </c>
@@ -11903,7 +11897,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>39</v>
       </c>
@@ -11934,9 +11928,9 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB9A2F52-9080-490D-91F1-658B5B0AADC8}">
   <dimension ref="A1:L26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -11944,7 +11938,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -11982,7 +11976,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -12020,7 +12014,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>121</v>
       </c>
@@ -12058,7 +12052,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>122</v>
       </c>
@@ -12096,7 +12090,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>123</v>
       </c>
@@ -12134,7 +12128,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>124</v>
       </c>
@@ -12172,7 +12166,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>125</v>
       </c>
@@ -12210,7 +12204,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>126</v>
       </c>
@@ -12248,7 +12242,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>21</v>
       </c>
@@ -12286,7 +12280,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>22</v>
       </c>
@@ -12324,7 +12318,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>23</v>
       </c>
@@ -12362,7 +12356,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>24</v>
       </c>
@@ -12411,7 +12405,7 @@
         <v>6.6666666666666666E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>25</v>
       </c>
@@ -12449,7 +12443,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>26</v>
       </c>
@@ -12472,7 +12466,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>115</v>
       </c>
@@ -12495,7 +12489,7 @@
         <v>8000</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>116</v>
       </c>
@@ -12518,7 +12512,7 @@
         <v>13600</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>117</v>
       </c>
@@ -12541,7 +12535,7 @@
         <v>5600</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>118</v>
       </c>
@@ -12564,7 +12558,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>119</v>
       </c>
@@ -12587,7 +12581,7 @@
         <v>40000</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>120</v>
       </c>

--- a/Solutions/Metabasite.xlsx
+++ b/Solutions/Metabasite.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hans\Documents\GitHub\Thermolab\Solutions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A47C9881-A06C-40B9-8B58-793F0A453D72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BACF93A1-08B3-4171-9E2C-C5B349629312}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19420" yWindow="3730" windowWidth="12630" windowHeight="16660" firstSheet="9" activeTab="14" xr2:uid="{A49E5DA2-E197-42C8-A9DC-E0DBAA94DA8C}"/>
+    <workbookView xWindow="1740" yWindow="850" windowWidth="24440" windowHeight="17520" activeTab="1" xr2:uid="{A49E5DA2-E197-42C8-A9DC-E0DBAA94DA8C}"/>
   </bookViews>
   <sheets>
     <sheet name="Amphibole" sheetId="1" r:id="rId1"/>
